--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3710,16 +3710,16 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1636174.68</v>
+        <v>1636338.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1249677.9</v>
+        <v>1249842.17</v>
       </c>
       <c r="S28" t="n">
-        <v>1310904.97</v>
+        <v>1311069.24</v>
       </c>
       <c r="T28" t="n">
-        <v>1434299.24</v>
+        <v>1434463.51</v>
       </c>
       <c r="U28" t="n">
         <v>61227.07</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
       </c>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16808,16 +16808,16 @@
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>133336049.87</v>
+        <v>133965299.87</v>
       </c>
       <c r="R139" t="n">
-        <v>103758007.13</v>
+        <v>104387257.13</v>
       </c>
       <c r="S139" t="n">
-        <v>106566937.33</v>
+        <v>107196187.33</v>
       </c>
       <c r="T139" t="n">
-        <v>116779802.81</v>
+        <v>117409052.81</v>
       </c>
       <c r="U139" t="n">
         <v>2808930.2</v>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17280,16 +17280,16 @@
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>31750960.63</v>
+        <v>32467200</v>
       </c>
       <c r="R143" t="n">
-        <v>31570960.63</v>
+        <v>32287200</v>
       </c>
       <c r="S143" t="n">
-        <v>31570960.63</v>
+        <v>32287200</v>
       </c>
       <c r="T143" t="n">
-        <v>31570960.63</v>
+        <v>32287200</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17566,7 +17566,7 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -17920,7 +17920,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>01/02/2026 08:28:06</t>
+          <t>02/02/2026 08:42:49</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12610,7 +12610,7 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13908,7 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15324,7 +15324,7 @@
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15442,7 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
       </c>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17212,7 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17448,7 +17448,7 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17566,7 +17566,7 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -17920,7 +17920,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>02/02/2026 08:42:49</t>
+          <t>02/02/2026 10:44:06</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF149"/>
+  <dimension ref="A1:AF150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,7 +692,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>156517.68</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>12545</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>12545</v>
       </c>
       <c r="O10" t="n">
         <v>542988.46</v>
@@ -1589,10 +1589,10 @@
         <v>3877150.67</v>
       </c>
       <c r="R10" t="n">
-        <v>60910.48</v>
+        <v>73455.48</v>
       </c>
       <c r="S10" t="n">
-        <v>60910.48</v>
+        <v>73455.48</v>
       </c>
       <c r="T10" t="n">
         <v>3334162.21</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1698,16 +1698,16 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>200000</v>
+        <v>200450</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>571611</v>
+        <v>572061</v>
       </c>
       <c r="R11" t="n">
-        <v>371611</v>
+        <v>371161</v>
       </c>
       <c r="S11" t="n">
         <v>371611</v>
@@ -1716,7 +1716,7 @@
         <v>371611</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="V11" t="n">
         <v>371611</v>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
         <v>4010</v>
       </c>
       <c r="G40" t="n">
-        <v>4470</v>
+        <v>4426</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -5126,34 +5126,34 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6558</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>6558</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>10494</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>6558</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3936</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>77329</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>22671</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>5</v>
@@ -5166,17 +5166,17 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5244,34 +5244,34 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>10494</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3936</v>
       </c>
       <c r="V41" t="n">
-        <v>635623</v>
+        <v>77329</v>
       </c>
       <c r="W41" t="n">
-        <v>821969</v>
+        <v>100000</v>
       </c>
       <c r="X41" t="n">
-        <v>186346</v>
+        <v>22671</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>821969</v>
+        <v>100000</v>
       </c>
       <c r="AA41" t="n">
         <v>5</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5362,34 +5362,34 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1087620.9</v>
+        <v>229579.78</v>
       </c>
       <c r="R42" t="n">
-        <v>450875.94</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>450875.94</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1087620.9</v>
+        <v>229579.78</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>16294924</v>
+        <v>635623</v>
       </c>
       <c r="W42" t="n">
-        <v>21072104</v>
+        <v>821969</v>
       </c>
       <c r="X42" t="n">
-        <v>4777180</v>
+        <v>186346</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>21072104</v>
+        <v>821969</v>
       </c>
       <c r="AA42" t="n">
         <v>5</v>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5458,11 +5458,11 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>5663.52</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5480,34 +5480,34 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>316616</v>
+        <v>1087620.9</v>
       </c>
       <c r="R43" t="n">
-        <v>316616</v>
+        <v>450875.94</v>
       </c>
       <c r="S43" t="n">
-        <v>316616</v>
+        <v>450875.94</v>
       </c>
       <c r="T43" t="n">
-        <v>316616</v>
+        <v>1087620.9</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>316616</v>
+        <v>16294924</v>
       </c>
       <c r="W43" t="n">
-        <v>316616</v>
+        <v>21072104</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4777180</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>316616</v>
+        <v>21072104</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5571,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -5598,25 +5598,25 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>316616</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>28666</v>
+        <v>316616</v>
       </c>
       <c r="W44" t="n">
-        <v>28666</v>
+        <v>316616</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>28666</v>
+        <v>316616</v>
       </c>
       <c r="AA44" t="n">
         <v>5</v>
@@ -5638,17 +5638,17 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
         <v>4010</v>
       </c>
       <c r="G45" t="n">
-        <v>7001</v>
+        <v>4470</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>44903900</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5731,10 +5731,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1000</v>
+        <v>28666</v>
       </c>
       <c r="W45" t="n">
-        <v>1000</v>
+        <v>28666</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1000</v>
+        <v>28666</v>
       </c>
       <c r="AA45" t="n">
         <v>5</v>
@@ -5761,12 +5761,12 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Material Permanente</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5795,19 +5795,19 @@
         <v>422</v>
       </c>
       <c r="F46" t="n">
-        <v>4018</v>
+        <v>4010</v>
       </c>
       <c r="G46" t="n">
-        <v>2431</v>
+        <v>7001</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CPPSR</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44903900</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5828,40 +5828,40 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4140329.7</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13165012.7</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>9024683</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>11429605.99</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>9024683</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2404922.99</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>9024683</v>
+        <v>1000</v>
       </c>
       <c r="W46" t="n">
-        <v>10590662</v>
+        <v>1000</v>
       </c>
       <c r="X46" t="n">
-        <v>1565979</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>10590662</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
         <v>5</v>
@@ -5869,7 +5869,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>População em Situação de Rua</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material Permanente</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5946,40 +5946,40 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4140329.7</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>13165012.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>9024683</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>11429605.99</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>9024683</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2404922.99</v>
       </c>
       <c r="V47" t="n">
-        <v>249936</v>
+        <v>9024683</v>
       </c>
       <c r="W47" t="n">
-        <v>293305</v>
+        <v>10590662</v>
       </c>
       <c r="X47" t="n">
-        <v>43369</v>
+        <v>1565979</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>293305</v>
+        <v>10590662</v>
       </c>
       <c r="AA47" t="n">
         <v>5</v>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6085,19 +6085,19 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>86656</v>
+        <v>249936</v>
       </c>
       <c r="W48" t="n">
-        <v>101693</v>
+        <v>293305</v>
       </c>
       <c r="X48" t="n">
-        <v>15037</v>
+        <v>43369</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>101693</v>
+        <v>293305</v>
       </c>
       <c r="AA48" t="n">
         <v>5</v>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -6188,34 +6188,34 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>48307</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>48307</v>
+        <v>86656</v>
       </c>
       <c r="W49" t="n">
-        <v>48307</v>
+        <v>101693</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>15037</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>48307</v>
+        <v>101693</v>
       </c>
       <c r="AA49" t="n">
         <v>5</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
         <v>4018</v>
       </c>
       <c r="G50" t="n">
-        <v>4321</v>
+        <v>2431</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -6306,34 +6306,34 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>48307</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>16354</v>
+        <v>48307</v>
       </c>
       <c r="W50" t="n">
-        <v>20000</v>
+        <v>48307</v>
       </c>
       <c r="X50" t="n">
-        <v>3646</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>20000</v>
+        <v>48307</v>
       </c>
       <c r="AA50" t="n">
         <v>5</v>
@@ -6346,17 +6346,17 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6424,34 +6424,34 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5686750</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5495750</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>10991500</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>5686750</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>5495750</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>18778855</v>
+        <v>16354</v>
       </c>
       <c r="W51" t="n">
-        <v>22965724</v>
+        <v>20000</v>
       </c>
       <c r="X51" t="n">
-        <v>4186869</v>
+        <v>3646</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>22965724</v>
+        <v>20000</v>
       </c>
       <c r="AA51" t="n">
         <v>5</v>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6506,16 +6506,16 @@
         <v>4018</v>
       </c>
       <c r="G52" t="n">
-        <v>9026</v>
+        <v>4321</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPPSR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>761377.5</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6542,34 +6542,34 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5686750</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>5495750</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>10991500</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>5686750</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>5495750</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>18778855</v>
       </c>
       <c r="W52" t="n">
-        <v>100000</v>
+        <v>22965724</v>
       </c>
       <c r="X52" t="n">
-        <v>100000</v>
+        <v>4186869</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>100000</v>
+        <v>22965724</v>
       </c>
       <c r="AA52" t="n">
         <v>5</v>
@@ -6577,7 +6577,7 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>População em Situação de Rua</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
         <v>4018</v>
       </c>
       <c r="G53" t="n">
-        <v>9040</v>
+        <v>9026</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -6678,16 +6678,16 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="X53" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AA53" t="n">
         <v>5</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
         <v>4018</v>
       </c>
       <c r="G54" t="n">
-        <v>9041</v>
+        <v>9040</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -6796,16 +6796,16 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="X54" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="Y54" t="n">
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="AA54" t="n">
         <v>5</v>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
         <v>4018</v>
       </c>
       <c r="G55" t="n">
-        <v>9042</v>
+        <v>9041</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -6914,16 +6914,16 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="X55" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="AA55" t="n">
         <v>5</v>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
         <v>4018</v>
       </c>
       <c r="G56" t="n">
-        <v>9043</v>
+        <v>9042</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7032,16 +7032,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="X56" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="AA56" t="n">
         <v>5</v>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
         <v>4018</v>
       </c>
       <c r="G57" t="n">
-        <v>9045</v>
+        <v>9043</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
         <v>4018</v>
       </c>
       <c r="G58" t="n">
-        <v>9046</v>
+        <v>9045</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -7268,16 +7268,16 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="X58" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>350000</v>
+        <v>100000</v>
       </c>
       <c r="AA58" t="n">
         <v>5</v>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
         <v>4018</v>
       </c>
       <c r="G59" t="n">
-        <v>9051</v>
+        <v>9046</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -7386,16 +7386,16 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="X59" t="n">
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>70000</v>
+        <v>350000</v>
       </c>
       <c r="AA59" t="n">
         <v>5</v>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
         <v>4018</v>
       </c>
       <c r="G60" t="n">
-        <v>9055</v>
+        <v>9051</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7504,16 +7504,16 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="X60" t="n">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>200000</v>
+        <v>70000</v>
       </c>
       <c r="AA60" t="n">
         <v>5</v>
@@ -7531,12 +7531,12 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         <v>4018</v>
       </c>
       <c r="G61" t="n">
-        <v>9097</v>
+        <v>9055</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7622,16 +7622,16 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2300000</v>
+        <v>200000</v>
       </c>
       <c r="X61" t="n">
-        <v>2300000</v>
+        <v>200000</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2300000</v>
+        <v>200000</v>
       </c>
       <c r="AA61" t="n">
         <v>5</v>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7683,19 +7683,19 @@
         <v>422</v>
       </c>
       <c r="F62" t="n">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="G62" t="n">
-        <v>4328</v>
+        <v>9097</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7722,34 +7722,34 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>627657</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1226000</v>
+        <v>2300000</v>
       </c>
       <c r="X62" t="n">
-        <v>598343</v>
+        <v>2300000</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1226000</v>
+        <v>2300000</v>
       </c>
       <c r="AA62" t="n">
         <v>5</v>
@@ -7757,7 +7757,7 @@
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7840,34 +7840,34 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>627657</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>25389</v>
+        <v>627657</v>
       </c>
       <c r="W63" t="n">
-        <v>49592</v>
+        <v>1226000</v>
       </c>
       <c r="X63" t="n">
-        <v>24203</v>
+        <v>598343</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>49592</v>
+        <v>1226000</v>
       </c>
       <c r="AA63" t="n">
         <v>5</v>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7958,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>868373</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -7967,25 +7967,25 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>868373</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>868373</v>
+        <v>25389</v>
       </c>
       <c r="W64" t="n">
-        <v>1696190</v>
+        <v>49592</v>
       </c>
       <c r="X64" t="n">
-        <v>827817</v>
+        <v>24203</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1696190</v>
+        <v>49592</v>
       </c>
       <c r="AA64" t="n">
         <v>5</v>
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>122450</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>122450</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8076,34 +8076,34 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>921519</v>
+        <v>868373</v>
       </c>
       <c r="R65" t="n">
-        <v>244900</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>244900</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>921519</v>
+        <v>868373</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>921519</v>
+        <v>868373</v>
       </c>
       <c r="W65" t="n">
-        <v>1800000</v>
+        <v>1696190</v>
       </c>
       <c r="X65" t="n">
-        <v>878481</v>
+        <v>827817</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1800000</v>
+        <v>1696190</v>
       </c>
       <c r="AA65" t="n">
         <v>5</v>
@@ -8121,12 +8121,12 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8155,19 +8155,19 @@
         <v>422</v>
       </c>
       <c r="F66" t="n">
-        <v>4023</v>
+        <v>4019</v>
       </c>
       <c r="G66" t="n">
-        <v>4320</v>
+        <v>4328</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CPPI</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>122450</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8185,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>122450</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8194,34 +8194,34 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>921519</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>244900</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>244900</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>921519</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>3000</v>
+        <v>921519</v>
       </c>
       <c r="W66" t="n">
-        <v>3000</v>
+        <v>1800000</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>878481</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>3000</v>
+        <v>1800000</v>
       </c>
       <c r="AA66" t="n">
         <v>5</v>
@@ -8229,7 +8229,7 @@
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Idoso</t>
+          <t>Criança e Adolescente</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
         <v>4023</v>
       </c>
       <c r="G67" t="n">
-        <v>4330</v>
+        <v>4320</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8312,34 +8312,34 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>1193451</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1193451</v>
+        <v>3000</v>
       </c>
       <c r="W67" t="n">
-        <v>1671844</v>
+        <v>3000</v>
       </c>
       <c r="X67" t="n">
-        <v>478393</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1671844</v>
+        <v>3000</v>
       </c>
       <c r="AA67" t="n">
         <v>5</v>
@@ -8357,12 +8357,12 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>245581.64</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -8430,34 +8430,34 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1193451</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>74955</v>
+        <v>1193451</v>
       </c>
       <c r="W68" t="n">
-        <v>105000</v>
+        <v>1671844</v>
       </c>
       <c r="X68" t="n">
-        <v>30045</v>
+        <v>478393</v>
       </c>
       <c r="Y68" t="n">
         <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>105000</v>
+        <v>1671844</v>
       </c>
       <c r="AA68" t="n">
         <v>5</v>
@@ -8475,12 +8475,12 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8563,19 +8563,19 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>616055</v>
+        <v>74955</v>
       </c>
       <c r="W69" t="n">
-        <v>863000</v>
+        <v>105000</v>
       </c>
       <c r="X69" t="n">
-        <v>246945</v>
+        <v>30045</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>863000</v>
+        <v>105000</v>
       </c>
       <c r="AA69" t="n">
         <v>5</v>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8666,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -8675,25 +8675,25 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>938683</v>
+        <v>616055</v>
       </c>
       <c r="W70" t="n">
-        <v>1314953</v>
+        <v>863000</v>
       </c>
       <c r="X70" t="n">
-        <v>376270</v>
+        <v>246945</v>
       </c>
       <c r="Y70" t="n">
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1314953</v>
+        <v>863000</v>
       </c>
       <c r="AA70" t="n">
         <v>5</v>
@@ -8711,12 +8711,12 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -8784,34 +8784,34 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21270</v>
+        <v>55000</v>
       </c>
       <c r="R71" t="n">
-        <v>21270</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>21270</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>21270</v>
+        <v>55000</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>21270</v>
+        <v>938683</v>
       </c>
       <c r="W71" t="n">
-        <v>21270</v>
+        <v>1314953</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>376270</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>21270</v>
+        <v>1314953</v>
       </c>
       <c r="AA71" t="n">
         <v>5</v>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8866,21 +8866,21 @@
         <v>4023</v>
       </c>
       <c r="G72" t="n">
-        <v>9028</v>
+        <v>4330</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPPI</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -8896,40 +8896,40 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>21720</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>20820</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>21270</v>
       </c>
       <c r="W72" t="n">
-        <v>100000</v>
+        <v>21270</v>
       </c>
       <c r="X72" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
         <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>100000</v>
+        <v>21270</v>
       </c>
       <c r="AA72" t="n">
         <v>5</v>
@@ -8937,22 +8937,22 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Idoso</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
         <v>4023</v>
       </c>
       <c r="G73" t="n">
-        <v>9038</v>
+        <v>9028</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>4023</v>
       </c>
       <c r="G74" t="n">
-        <v>9050</v>
+        <v>9038</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -9156,16 +9156,16 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X74" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA74" t="n">
         <v>5</v>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9217,14 +9217,14 @@
         <v>422</v>
       </c>
       <c r="F75" t="n">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="G75" t="n">
-        <v>2051</v>
+        <v>9050</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9256,34 +9256,34 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>679177.12</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>1838981</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>2107032</v>
+        <v>75000</v>
       </c>
       <c r="X75" t="n">
-        <v>268051</v>
+        <v>75000</v>
       </c>
       <c r="Y75" t="n">
         <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2107032</v>
+        <v>75000</v>
       </c>
       <c r="AA75" t="n">
         <v>5</v>
@@ -9291,7 +9291,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9374,34 +9374,34 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>679177.12</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>69823</v>
+        <v>1838981</v>
       </c>
       <c r="W76" t="n">
-        <v>80000</v>
+        <v>2107032</v>
       </c>
       <c r="X76" t="n">
-        <v>10177</v>
+        <v>268051</v>
       </c>
       <c r="Y76" t="n">
         <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>80000</v>
+        <v>2107032</v>
       </c>
       <c r="AA76" t="n">
         <v>5</v>
@@ -9419,12 +9419,12 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9507,19 +9507,19 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>130917</v>
+        <v>69823</v>
       </c>
       <c r="W77" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="X77" t="n">
-        <v>19083</v>
+        <v>10177</v>
       </c>
       <c r="Y77" t="n">
         <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="AA77" t="n">
         <v>5</v>
@@ -9537,12 +9537,12 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9610,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -9619,25 +9619,25 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>392752</v>
+        <v>130917</v>
       </c>
       <c r="W78" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="X78" t="n">
-        <v>57248</v>
+        <v>19083</v>
       </c>
       <c r="Y78" t="n">
         <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>450000</v>
+        <v>150000</v>
       </c>
       <c r="AA78" t="n">
         <v>5</v>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9692,16 +9692,16 @@
         <v>4024</v>
       </c>
       <c r="G79" t="n">
-        <v>2142</v>
+        <v>2051</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>EDH</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9725,10 +9725,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>49471</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -9737,25 +9737,25 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>50000</v>
+        <v>392752</v>
       </c>
       <c r="W79" t="n">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="X79" t="n">
-        <v>49471</v>
+        <v>57248</v>
       </c>
       <c r="Y79" t="n">
         <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>50000</v>
+        <v>450000</v>
       </c>
       <c r="AA79" t="n">
         <v>5</v>
@@ -9763,7 +9763,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Educação em Direitos Humanos</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9843,7 +9843,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>49471</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -9861,19 +9861,19 @@
         <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>1058</v>
+        <v>50000</v>
       </c>
       <c r="W80" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="X80" t="n">
-        <v>98942</v>
+        <v>49471</v>
       </c>
       <c r="Y80" t="n">
         <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="AA80" t="n">
         <v>5</v>
@@ -9891,12 +9891,12 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9961,7 +9961,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>49471</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -9979,19 +9979,19 @@
         <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>50000</v>
+        <v>1058</v>
       </c>
       <c r="W81" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="X81" t="n">
-        <v>49471</v>
+        <v>98942</v>
       </c>
       <c r="Y81" t="n">
         <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="AA81" t="n">
         <v>5</v>
@@ -10009,12 +10009,12 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10079,7 +10079,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>49471</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -10097,19 +10097,19 @@
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>13341</v>
+        <v>50000</v>
       </c>
       <c r="W82" t="n">
-        <v>1261000</v>
+        <v>50000</v>
       </c>
       <c r="X82" t="n">
-        <v>1247659</v>
+        <v>49471</v>
       </c>
       <c r="Y82" t="n">
         <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1261000</v>
+        <v>50000</v>
       </c>
       <c r="AA82" t="n">
         <v>5</v>
@@ -10127,12 +10127,12 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10164,16 +10164,16 @@
         <v>4024</v>
       </c>
       <c r="G83" t="n">
-        <v>3406</v>
+        <v>2142</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Selo DH</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>44903900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10215,19 +10215,19 @@
         <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1000</v>
+        <v>13341</v>
       </c>
       <c r="W83" t="n">
-        <v>1000</v>
+        <v>1261000</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1247659</v>
       </c>
       <c r="Y83" t="n">
         <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1000</v>
+        <v>1261000</v>
       </c>
       <c r="AA83" t="n">
         <v>5</v>
@@ -10235,7 +10235,7 @@
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Selo DH</t>
+          <t>Educação em Direitos Humanos</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10282,16 +10282,16 @@
         <v>4024</v>
       </c>
       <c r="G84" t="n">
-        <v>4314</v>
+        <v>3406</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Desaparecidas</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44903900</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10333,19 +10333,19 @@
         <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W84" t="n">
-        <v>550500</v>
+        <v>1000</v>
       </c>
       <c r="X84" t="n">
-        <v>550500</v>
+        <v>0</v>
       </c>
       <c r="Y84" t="n">
         <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>550500</v>
+        <v>1000</v>
       </c>
       <c r="AA84" t="n">
         <v>5</v>
@@ -10353,7 +10353,7 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Desaparecidos</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Material Permanente</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10400,16 +10400,16 @@
         <v>4024</v>
       </c>
       <c r="G85" t="n">
-        <v>4317</v>
+        <v>4314</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>DMV</t>
+          <t>Desaparecidas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10451,19 +10451,19 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1000</v>
+        <v>550500</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>550500</v>
       </c>
       <c r="Y85" t="n">
         <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1000</v>
+        <v>550500</v>
       </c>
       <c r="AA85" t="n">
         <v>5</v>
@@ -10471,7 +10471,7 @@
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Memória e Verdade</t>
+          <t>Desaparecidos</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10518,16 +10518,16 @@
         <v>4024</v>
       </c>
       <c r="G86" t="n">
-        <v>4318</v>
+        <v>4317</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>DMV</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10554,25 +10554,25 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>12675633</v>
+        <v>1000</v>
       </c>
       <c r="W86" t="n">
-        <v>12675633</v>
+        <v>1000</v>
       </c>
       <c r="X86" t="n">
         <v>0</v>
@@ -10581,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>12675633</v>
+        <v>1000</v>
       </c>
       <c r="AA86" t="n">
         <v>5</v>
@@ -10589,7 +10589,7 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Memória e Verdade</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10672,25 +10672,25 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="W87" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
@@ -10699,7 +10699,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AA87" t="n">
         <v>5</v>
@@ -10717,12 +10717,12 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10805,10 +10805,10 @@
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="W88" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
@@ -10817,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AA88" t="n">
         <v>5</v>
@@ -10835,12 +10835,12 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10872,16 +10872,16 @@
         <v>4024</v>
       </c>
       <c r="G89" t="n">
-        <v>4319</v>
+        <v>4318</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10923,19 +10923,19 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="W89" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="X89" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AA89" t="n">
         <v>5</v>
@@ -10943,7 +10943,7 @@
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -10953,12 +10953,12 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -10999,12 +10999,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -11041,19 +11041,19 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="W90" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AA90" t="n">
         <v>5</v>
@@ -11066,17 +11066,17 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11117,12 +11117,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -11153,25 +11153,25 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="W91" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="X91" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AA91" t="n">
         <v>5</v>
@@ -11184,17 +11184,17 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11226,16 +11226,16 @@
         <v>4024</v>
       </c>
       <c r="G92" t="n">
-        <v>4324</v>
+        <v>4319</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11262,34 +11262,34 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="W92" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="X92" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AA92" t="n">
         <v>5</v>
@@ -11297,7 +11297,7 @@
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -11398,16 +11398,16 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Y93" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AA93" t="n">
         <v>5</v>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -11486,7 +11486,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -11513,19 +11513,19 @@
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X94" t="n">
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Z94" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>5</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AE95" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -11722,7 +11722,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -11749,7 +11749,7 @@
         <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
@@ -11761,7 +11761,7 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA96" t="n">
         <v>5</v>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AE96" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11816,11 +11816,11 @@
         <v>4024</v>
       </c>
       <c r="G97" t="n">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11830,7 +11830,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -11840,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -11867,10 +11867,10 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W97" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
         <v>0</v>
@@ -11879,7 +11879,7 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA97" t="n">
         <v>5</v>
@@ -11887,12 +11887,12 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -11934,16 +11934,16 @@
         <v>4024</v>
       </c>
       <c r="G98" t="n">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11970,25 +11970,25 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="W98" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X98" t="n">
         <v>0</v>
@@ -11997,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AA98" t="n">
         <v>5</v>
@@ -12005,7 +12005,7 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1054150.07</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -12088,25 +12088,25 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="W99" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -12115,7 +12115,7 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AA99" t="n">
         <v>5</v>
@@ -12133,12 +12133,12 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12206,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -12215,16 +12215,16 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="W100" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AA100" t="n">
         <v>5</v>
@@ -12251,12 +12251,12 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12288,16 +12288,16 @@
         <v>4024</v>
       </c>
       <c r="G101" t="n">
-        <v>4332</v>
+        <v>4326</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12324,25 +12324,25 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5238691</v>
+        <v>6926170.67</v>
       </c>
       <c r="R101" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>8823589.4</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>5238691</v>
+        <v>6926170.67</v>
       </c>
       <c r="U101" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="W101" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -12351,7 +12351,7 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AA101" t="n">
         <v>5</v>
@@ -12359,7 +12359,7 @@
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12442,25 +12442,25 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>5238691</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>8823589.4</v>
       </c>
       <c r="T102" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="V102" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="W102" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -12469,7 +12469,7 @@
         <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AA102" t="n">
         <v>5</v>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12524,16 +12524,16 @@
         <v>4024</v>
       </c>
       <c r="G103" t="n">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12560,7 +12560,7 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -12569,16 +12569,16 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="W103" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
@@ -12587,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="AA103" t="n">
         <v>5</v>
@@ -12595,7 +12595,7 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -12605,12 +12605,12 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12651,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12678,7 +12678,7 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -12687,16 +12687,16 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="W104" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -12705,7 +12705,7 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="AA104" t="n">
         <v>5</v>
@@ -12723,12 +12723,12 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -12790,31 +12790,31 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>46120</v>
+        <v>13728.92</v>
       </c>
       <c r="R105" t="n">
-        <v>43870</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>45670</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>44320</v>
+        <v>13728.92</v>
       </c>
       <c r="U105" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="W105" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -12823,7 +12823,7 @@
         <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="AA105" t="n">
         <v>5</v>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12878,21 +12878,21 @@
         <v>4024</v>
       </c>
       <c r="G106" t="n">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -12908,31 +12908,31 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>47920</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>43870</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="V106" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="W106" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -12941,7 +12941,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="AA106" t="n">
         <v>5</v>
@@ -12949,22 +12949,22 @@
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -12993,14 +12993,14 @@
         <v>422</v>
       </c>
       <c r="F107" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G107" t="n">
-        <v>2053</v>
+        <v>4335</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -13014,7 +13014,7 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>4887292</v>
+        <v>50000</v>
       </c>
       <c r="W107" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="X107" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="AA107" t="n">
         <v>5</v>
@@ -13067,7 +13067,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13128,11 +13128,11 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -13141,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13150,34 +13150,34 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="W108" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="X108" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="AA108" t="n">
         <v>5</v>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13241,12 +13241,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -13268,34 +13268,34 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="X109" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AA109" t="n">
         <v>5</v>
@@ -13308,17 +13308,17 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13386,34 +13386,34 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>519437</v>
+        <v>150755</v>
       </c>
       <c r="W110" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="X110" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="AA110" t="n">
         <v>5</v>
@@ -13431,12 +13431,12 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13498,40 +13498,40 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>139083</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>4701261</v>
+        <v>519437</v>
       </c>
       <c r="W111" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="X111" t="n">
-        <v>251895</v>
+        <v>27832</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="AA111" t="n">
         <v>5</v>
@@ -13549,12 +13549,12 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -13616,40 +13616,40 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>282533</v>
+        <v>139083</v>
       </c>
       <c r="R112" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="S112" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="T112" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>282533</v>
+        <v>4701261</v>
       </c>
       <c r="W112" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>251895</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="AA112" t="n">
         <v>5</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13713,12 +13713,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -13740,34 +13740,34 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="W113" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="X113" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="AA113" t="n">
         <v>5</v>
@@ -13780,17 +13780,17 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13822,7 @@
         <v>4025</v>
       </c>
       <c r="G114" t="n">
-        <v>4329</v>
+        <v>2053</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -13849,7 +13849,7 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -13858,34 +13858,34 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
-        <v>2356400</v>
+        <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="X114" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="AA114" t="n">
         <v>5</v>
@@ -13903,12 +13903,12 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
         <v>4025</v>
       </c>
       <c r="G115" t="n">
-        <v>6178</v>
+        <v>4329</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13958,7 +13958,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -13967,43 +13967,43 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="O115" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="R115" t="n">
-        <v>21164757.5</v>
+        <v>1576800</v>
       </c>
       <c r="S115" t="n">
-        <v>21344367.15</v>
+        <v>2356400</v>
       </c>
       <c r="T115" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="U115" t="n">
-        <v>179609.65</v>
+        <v>779600</v>
       </c>
       <c r="V115" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="W115" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="AA115" t="n">
         <v>5</v>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14088,31 +14088,31 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>106229.82</v>
+        <v>23851875.51</v>
       </c>
       <c r="R116" t="n">
-        <v>16178</v>
+        <v>21164757.5</v>
       </c>
       <c r="S116" t="n">
-        <v>17972</v>
+        <v>21344367.15</v>
       </c>
       <c r="T116" t="n">
-        <v>106229.82</v>
+        <v>22426358</v>
       </c>
       <c r="U116" t="n">
-        <v>1794</v>
+        <v>179609.65</v>
       </c>
       <c r="V116" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="W116" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -14121,7 +14121,7 @@
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AA116" t="n">
         <v>5</v>
@@ -14139,12 +14139,12 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14212,25 +14212,25 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>88531.96000000001</v>
+        <v>106229.82</v>
       </c>
       <c r="R117" t="n">
-        <v>88531.96000000001</v>
+        <v>62133</v>
       </c>
       <c r="S117" t="n">
-        <v>88531.96000000001</v>
+        <v>63927</v>
       </c>
       <c r="T117" t="n">
-        <v>88531.96000000001</v>
+        <v>106229.82</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="V117" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="W117" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -14239,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AA117" t="n">
         <v>5</v>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14330,25 +14330,25 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>306807.5</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="S118" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="T118" t="n">
-        <v>306807.5</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="W118" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14357,7 +14357,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AA118" t="n">
         <v>5</v>
@@ -14375,12 +14375,12 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -14448,25 +14448,25 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>988754.48</v>
+        <v>364021.94</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="T119" t="n">
-        <v>988754.48</v>
+        <v>364021.94</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="W119" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -14475,7 +14475,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AA119" t="n">
         <v>5</v>
@@ -14493,12 +14493,12 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -14566,25 +14566,25 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>80000</v>
+        <v>988754.48</v>
       </c>
       <c r="R120" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>80000</v>
+        <v>988754.48</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="W120" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -14593,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AA120" t="n">
         <v>5</v>
@@ -14606,7 +14606,7 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14657,12 +14657,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -14684,25 +14684,25 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="R121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="S121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="T121" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="W121" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -14711,7 +14711,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AA121" t="n">
         <v>5</v>
@@ -14724,17 +14724,17 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14766,16 +14766,16 @@
         <v>4025</v>
       </c>
       <c r="G122" t="n">
-        <v>9027</v>
+        <v>6178</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14784,7 +14784,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -14802,34 +14802,34 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="W122" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X122" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AA122" t="n">
         <v>5</v>
@@ -14837,7 +14837,7 @@
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -14847,12 +14847,12 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
         <v>4025</v>
       </c>
       <c r="G123" t="n">
-        <v>9030</v>
+        <v>9027</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -14938,16 +14938,16 @@
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X123" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
         <v>4025</v>
       </c>
       <c r="G124" t="n">
-        <v>9044</v>
+        <v>9030</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -15056,16 +15056,16 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X124" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA124" t="n">
         <v>5</v>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15117,19 +15117,19 @@
         <v>422</v>
       </c>
       <c r="F125" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G125" t="n">
-        <v>4327</v>
+        <v>9044</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -15171,19 +15171,19 @@
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="AA125" t="n">
         <v>5</v>
@@ -15191,7 +15191,7 @@
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15238,7 @@
         <v>4026</v>
       </c>
       <c r="G126" t="n">
-        <v>4334</v>
+        <v>4327</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15274,34 +15274,34 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>3469273</v>
+        <v>11949</v>
       </c>
       <c r="W126" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="X126" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AA126" t="n">
         <v>5</v>
@@ -15319,12 +15319,12 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -15392,34 +15392,34 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>5374</v>
+        <v>3469273</v>
       </c>
       <c r="W127" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="X127" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AA127" t="n">
         <v>5</v>
@@ -15437,12 +15437,12 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -15525,19 +15525,19 @@
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="W128" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="X128" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AA128" t="n">
         <v>5</v>
@@ -15555,12 +15555,12 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -15628,7 +15628,7 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -15637,25 +15637,25 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="W129" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="X129" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AA129" t="n">
         <v>5</v>
@@ -15673,12 +15673,12 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -15746,7 +15746,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>225</v>
+        <v>4890595.9</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -15755,25 +15755,25 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>225</v>
+        <v>4890595.9</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="W130" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AA130" t="n">
         <v>5</v>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -15796,7 +15796,7 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15828,21 +15828,21 @@
         <v>4026</v>
       </c>
       <c r="G131" t="n">
-        <v>9025</v>
+        <v>4334</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -15864,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -15873,25 +15873,25 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W131" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="X131" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="AA131" t="n">
         <v>5</v>
@@ -15899,22 +15899,22 @@
       <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -15940,22 +15940,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F132" t="n">
         <v>4026</v>
       </c>
       <c r="G132" t="n">
-        <v>4322</v>
+        <v>9025</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -15997,19 +15997,19 @@
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>7143</v>
+        <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="X132" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="AA132" t="n">
         <v>5</v>
@@ -16017,7 +16017,7 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -16027,12 +16027,12 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16100,7 +16100,7 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0</v>
@@ -16109,25 +16109,25 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>33669</v>
+        <v>7143</v>
       </c>
       <c r="W133" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="X133" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AA133" t="n">
         <v>5</v>
@@ -16145,12 +16145,12 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16182,16 +16182,16 @@
         <v>4026</v>
       </c>
       <c r="G134" t="n">
-        <v>9234</v>
+        <v>4322</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -16227,25 +16227,25 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="W134" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="X134" t="n">
-        <v>100000</v>
+        <v>187297</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="AA134" t="n">
         <v>5</v>
@@ -16253,7 +16253,7 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -16263,12 +16263,12 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16280,12 +16280,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16294,22 +16294,22 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F135" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G135" t="n">
-        <v>4426</v>
+        <v>9234</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -16354,16 +16354,16 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="X135" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="AA135" t="n">
         <v>5</v>
@@ -16371,7 +16371,7 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -16381,53 +16381,53 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F136" t="n">
         <v>4010</v>
       </c>
       <c r="G136" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -16436,7 +16436,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>3235052.09</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -16454,34 +16454,34 @@
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AA136" t="n">
         <v>5</v>
@@ -16499,12 +16499,12 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -16554,7 +16554,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>6470104.18</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -16572,34 +16572,34 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="W137" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="X137" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AA137" t="n">
         <v>5</v>
@@ -16617,12 +16617,12 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16644,21 +16644,21 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F138" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G138" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -16705,19 +16705,19 @@
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="W138" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AA138" t="n">
         <v>5</v>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F139" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G139" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -16790,7 +16790,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>438463.7</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -16802,40 +16802,40 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>16556247.06</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>133965299.87</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>104387257.13</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>107196187.33</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>117409052.81</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>2808930.2</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>166077092</v>
+        <v>1000</v>
       </c>
       <c r="W139" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="X139" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="AA139" t="n">
         <v>5</v>
@@ -16853,12 +16853,12 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -16899,16 +16899,16 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>18196243.45</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -16920,40 +16920,40 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>18089870.01</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>137033545.77</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>105921880.08</v>
       </c>
       <c r="S140" t="n">
-        <v>0</v>
+        <v>108730810.28</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>118943675.76</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>2808930.2</v>
       </c>
       <c r="V140" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="W140" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AA140" t="n">
         <v>5</v>
@@ -16966,17 +16966,17 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -17059,10 +17059,10 @@
         <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="W141" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X141" t="n">
         <v>0</v>
@@ -17071,7 +17071,7 @@
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AA141" t="n">
         <v>5</v>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic. de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17135,16 +17135,16 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -17156,40 +17156,40 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>52634438.4</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="W142" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="X142" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AA142" t="n">
         <v>5</v>
@@ -17202,17 +17202,17 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>PMSP-SMDHC-Fundo Munic. de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17253,7 +17253,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -17262,7 +17262,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>5410565.4</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -17274,40 +17274,40 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>180000</v>
+        <v>26317219.2</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>32467200</v>
+        <v>52634438.4</v>
       </c>
       <c r="R143" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="S143" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="T143" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>80849746</v>
+        <v>136889022</v>
       </c>
       <c r="W143" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="X143" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="AA143" t="n">
         <v>5</v>
@@ -17325,12 +17325,12 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17376,11 +17376,11 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>2304000</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -17392,40 +17392,40 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>32467200</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="S144" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>2000</v>
+        <v>80849746</v>
       </c>
       <c r="W144" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="AA144" t="n">
         <v>5</v>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
@@ -17448,19 +17448,19 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -17474,27 +17474,27 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F145" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G145" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -17531,10 +17531,10 @@
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="W145" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X145" t="n">
         <v>0</v>
@@ -17543,7 +17543,7 @@
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -17551,22 +17551,22 @@
       <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17607,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -17649,10 +17649,10 @@
         <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="W146" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AA146" t="n">
         <v>5</v>
@@ -17679,12 +17679,12 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17710,22 +17710,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F147" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G147" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -17767,10 +17767,10 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="W147" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -17779,7 +17779,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -17787,7 +17787,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -17797,12 +17797,12 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17828,27 +17828,27 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F148" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G148" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -17885,10 +17885,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -17897,7 +17897,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -17905,22 +17905,22 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Sem detalhamento</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serv. de Tec. da Inf. e Com - PJ</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>02/02/2026 10:44:06</t>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>
@@ -17966,11 +17966,11 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="K149" t="n">
-        <v>1433738.57</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -17982,31 +17982,31 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>35187195.47</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>31855789.6</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>33468553.7</v>
+        <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>32118763.49</v>
+        <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18015,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18028,17 +18028,135 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>03/02/2026 10:42:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>422</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G150" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>4254945.75</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>35187195.47</v>
+      </c>
+      <c r="R150" t="n">
+        <v>31855789.6</v>
+      </c>
+      <c r="S150" t="n">
+        <v>33468553.7</v>
+      </c>
+      <c r="T150" t="n">
+        <v>32118763.49</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V150" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W150" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
+      <c r="AE150" t="inlineStr">
         <is>
           <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>02/02/2026 10:44:06</t>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>03/02/2026 10:42:17</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF150"/>
+  <dimension ref="A1:AG150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,15 +564,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>acao_programatica</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>nome_elemento</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>ds_fonte</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>nome_elemento</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>data_hora_extracao</t>
         </is>
@@ -682,17 +687,22 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>Conselho</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Material de Consumo</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUNDO MUNICIPAL DO IDOSO-FMID</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Material de Consumo</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -742,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>156517.68</v>
+        <v>264605.68</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -760,16 +770,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4784344.21</v>
+        <v>5256476.99</v>
       </c>
       <c r="R3" t="n">
-        <v>4509695.21</v>
+        <v>4540095.21</v>
       </c>
       <c r="S3" t="n">
-        <v>4509695.21</v>
+        <v>4540095.21</v>
       </c>
       <c r="T3" t="n">
-        <v>4784344.21</v>
+        <v>5256476.99</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -800,17 +810,22 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>FMID</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUNDO MUNICIPAL DO IDOSO-FMID</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -918,7 +933,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Formação</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -928,7 +943,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1056,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1046,7 +1066,12 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1179,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1164,7 +1189,12 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1302,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1282,7 +1312,12 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1367,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>11257.26</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1390,7 +1425,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1400,7 +1435,12 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1548,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1518,7 +1558,12 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1589,10 +1634,10 @@
         <v>3877150.67</v>
       </c>
       <c r="R10" t="n">
-        <v>73455.48</v>
+        <v>87583.42999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>73455.48</v>
+        <v>87583.42999999999</v>
       </c>
       <c r="T10" t="n">
         <v>3334162.21</v>
@@ -1626,7 +1671,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1636,7 +1681,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1736,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>107.79</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1707,10 +1757,10 @@
         <v>572061</v>
       </c>
       <c r="R11" t="n">
-        <v>371161</v>
+        <v>371611</v>
       </c>
       <c r="S11" t="n">
-        <v>371611</v>
+        <v>372061</v>
       </c>
       <c r="T11" t="n">
         <v>371611</v>
@@ -1744,17 +1794,22 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1917,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -1872,7 +1927,12 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>178219.94</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1943,10 +2003,10 @@
         <v>193219.94</v>
       </c>
       <c r="R13" t="n">
-        <v>178219.94</v>
+        <v>193219.94</v>
       </c>
       <c r="S13" t="n">
-        <v>178219.94</v>
+        <v>193219.94</v>
       </c>
       <c r="T13" t="n">
         <v>193219.94</v>
@@ -1980,7 +2040,7 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -1990,7 +2050,12 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2163,7 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2108,7 +2173,12 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2286,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2226,7 +2296,12 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2409,7 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2344,7 +2419,12 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2532,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ADM - CIEE</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
@@ -2462,7 +2542,12 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2655,7 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -2580,7 +2665,12 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2648,16 +2738,16 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>767852.36</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>405385.74</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>405385.74</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>767852.36</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2688,7 +2778,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -2698,7 +2788,12 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2901,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -2816,7 +2911,12 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -2924,7 +3024,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia - Comunicação</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -2934,7 +3034,12 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3147,7 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia - Comunicação</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3052,7 +3157,12 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3270,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia - Comunicação</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3170,7 +3280,12 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3393,7 @@
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -3288,7 +3403,12 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3516,7 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -3406,7 +3526,12 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3639,7 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -3524,7 +3649,12 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3762,7 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3642,7 +3772,12 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>110.08</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3710,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1636338.95</v>
+        <v>1687764.06</v>
       </c>
       <c r="R28" t="n">
         <v>1249842.17</v>
@@ -3719,7 +3854,7 @@
         <v>1311069.24</v>
       </c>
       <c r="T28" t="n">
-        <v>1434463.51</v>
+        <v>1485888.62</v>
       </c>
       <c r="U28" t="n">
         <v>61227.07</v>
@@ -3750,7 +3885,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -3760,7 +3895,12 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3868,7 +4008,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -3878,7 +4018,12 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4131,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -3996,7 +4141,12 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4104,17 +4254,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
+          <t>CT - Administração</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4377,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -4232,7 +4387,12 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4500,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -4350,7 +4510,12 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4565,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1003.1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4421,10 +4586,10 @@
         <v>5916961.44</v>
       </c>
       <c r="R34" t="n">
-        <v>49943.26</v>
+        <v>2981862.7</v>
       </c>
       <c r="S34" t="n">
-        <v>49943.26</v>
+        <v>2981862.7</v>
       </c>
       <c r="T34" t="n">
         <v>2985047</v>
@@ -4458,7 +4623,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -4468,7 +4633,12 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4746,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CT - Administração</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -4586,7 +4756,12 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4869,7 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -4704,7 +4879,12 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4992,7 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Cooperação Técnica Internacional</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -4822,7 +5002,12 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -4930,7 +5115,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -4940,7 +5125,12 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5048,17 +5238,22 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
+          <t>Sesana - Políticas</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5166,17 +5361,22 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
+          <t>Sesana - Políticas</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Obras e Instalações</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>Obras e Instalações</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5484,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -5294,7 +5494,12 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5607,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -5412,7 +5617,12 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5730,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -5530,7 +5740,12 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5638,17 +5853,22 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
+          <t>Sesana - Cresan</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5976,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Cresan</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -5766,7 +5986,12 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5874,7 +6099,7 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
@@ -5884,7 +6109,12 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6222,7 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
@@ -6002,7 +6232,12 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6345,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
@@ -6120,7 +6355,12 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6468,7 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Equipamentos</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -6238,7 +6478,12 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6346,17 +6591,22 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
+          <t>CPPSR - Equipamentos</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6714,7 @@
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Políticas</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -6474,7 +6724,12 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6837,7 @@
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPSR - Políticas</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
@@ -6592,7 +6847,12 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6960,7 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
@@ -6710,7 +6970,12 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7083,7 @@
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
@@ -6828,7 +7093,12 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -6936,7 +7206,7 @@
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
@@ -6946,7 +7216,12 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7329,7 @@
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
@@ -7064,7 +7339,12 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7172,7 +7452,7 @@
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -7182,7 +7462,12 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7575,7 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -7300,7 +7585,12 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7698,7 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -7418,7 +7708,12 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7821,7 @@
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
@@ -7536,7 +7831,12 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7944,7 @@
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
@@ -7654,7 +7954,12 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7762,7 +8067,7 @@
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
@@ -7772,7 +8077,12 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7880,7 +8190,7 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -7890,7 +8200,12 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -7998,7 +8313,7 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -8008,7 +8323,12 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8436,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -8126,7 +8446,12 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8559,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPCA</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -8244,7 +8569,12 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8682,7 @@
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Políticas</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
@@ -8362,7 +8692,12 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8805,7 @@
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
@@ -8480,7 +8815,12 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8928,7 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -8598,7 +8938,12 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8706,7 +9051,7 @@
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
@@ -8716,7 +9061,12 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8824,7 +9174,7 @@
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPPI - Equipamentos</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
@@ -8834,7 +9184,12 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -8905,10 +9260,10 @@
         <v>21720</v>
       </c>
       <c r="R72" t="n">
-        <v>20820</v>
+        <v>21270</v>
       </c>
       <c r="S72" t="n">
-        <v>21270</v>
+        <v>21720</v>
       </c>
       <c r="T72" t="n">
         <v>21270</v>
@@ -8942,17 +9297,22 @@
       </c>
       <c r="AD72" t="inlineStr">
         <is>
+          <t>CPPI - Equipamentos</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9420,7 @@
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -9070,7 +9430,12 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9543,7 @@
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -9188,7 +9553,12 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9666,7 @@
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
@@ -9306,7 +9676,12 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9789,7 @@
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -9424,7 +9799,12 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9912,7 @@
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
@@ -9542,7 +9922,12 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9650,7 +10035,7 @@
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
@@ -9660,7 +10045,12 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9768,7 +10158,7 @@
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Equipamentos</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -9778,7 +10168,12 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -9886,7 +10281,7 @@
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
@@ -9896,7 +10291,12 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10404,7 @@
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
@@ -10014,7 +10414,12 @@
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10527,7 @@
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -10132,7 +10537,12 @@
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10650,7 @@
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>EDH</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
@@ -10250,7 +10660,12 @@
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10773,7 @@
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Selo DH</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr">
@@ -10368,7 +10783,12 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10896,7 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Desaparecidas</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -10486,7 +10906,12 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10594,7 +11019,7 @@
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>DMV</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
@@ -10604,7 +11029,12 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10654,7 +11084,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>2459898.9</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -10672,7 +11102,7 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2861229.41</v>
+        <v>10919153.01</v>
       </c>
       <c r="R87" t="n">
         <v>2861229.41</v>
@@ -10681,7 +11111,7 @@
         <v>2861229.41</v>
       </c>
       <c r="T87" t="n">
-        <v>2861229.41</v>
+        <v>10919153.01</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -10712,7 +11142,7 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -10722,7 +11152,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10830,7 +11265,7 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -10840,7 +11275,12 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -10948,7 +11388,7 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
@@ -10958,7 +11398,12 @@
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11511,7 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -11076,7 +11521,12 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11184,17 +11634,22 @@
       </c>
       <c r="AD91" t="inlineStr">
         <is>
+          <t>CPLGBTI - Políticas</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
           <t>Código Genérico</t>
         </is>
       </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11757,7 @@
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
@@ -11312,7 +11767,12 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11420,7 +11880,7 @@
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -11430,7 +11890,12 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11538,17 +12003,22 @@
       </c>
       <c r="AD94" t="inlineStr">
         <is>
+          <t>CPIPTD - Políticas</t>
+        </is>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11656,17 +12126,22 @@
       </c>
       <c r="AD95" t="inlineStr">
         <is>
+          <t>CPIPTD - Políticas</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11774,17 +12249,22 @@
       </c>
       <c r="AD96" t="inlineStr">
         <is>
+          <t>CPIPTD - Políticas</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -11892,17 +12372,22 @@
       </c>
       <c r="AD97" t="inlineStr">
         <is>
+          <t>CPIPTD - Políticas</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
           <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12495,7 @@
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -12020,7 +12505,12 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12618,7 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
@@ -12138,7 +12628,12 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12741,7 @@
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
@@ -12256,7 +12751,12 @@
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12864,7 @@
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
@@ -12374,7 +12874,12 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12929,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>483294.93</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -12482,7 +12987,7 @@
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
@@ -12492,7 +12997,12 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12600,7 +13110,7 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
@@ -12610,7 +13120,12 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12718,7 +13233,7 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
@@ -12728,7 +13243,12 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12836,7 +13356,7 @@
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
@@ -12846,7 +13366,12 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -12917,10 +13442,10 @@
         <v>47920</v>
       </c>
       <c r="R106" t="n">
-        <v>43870</v>
+        <v>45670</v>
       </c>
       <c r="S106" t="n">
-        <v>45670</v>
+        <v>47470</v>
       </c>
       <c r="T106" t="n">
         <v>45670</v>
@@ -12954,17 +13479,22 @@
       </c>
       <c r="AD106" t="inlineStr">
         <is>
+          <t>CPDDH</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13072,7 +13602,7 @@
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
@@ -13082,7 +13612,12 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13667,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>814548.67</v>
+        <v>1221823</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -13190,7 +13725,7 @@
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13200,7 +13735,12 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13308,17 +13848,22 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
+          <t>CPM - CMB</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
           <t>Código Genérico</t>
         </is>
       </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13426,7 +13971,7 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
@@ -13436,7 +13981,12 @@
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13544,7 +14094,7 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
@@ -13554,7 +14104,12 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13662,7 +14217,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -13672,7 +14227,12 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13780,17 +14340,22 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
+          <t>CPM - CMB</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -13898,7 +14463,7 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
@@ -13908,7 +14473,12 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14016,7 +14586,7 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
@@ -14026,7 +14596,12 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14651,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>333946.2</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -14097,16 +14672,16 @@
         <v>23851875.51</v>
       </c>
       <c r="R116" t="n">
-        <v>21164757.5</v>
+        <v>21820108.89</v>
       </c>
       <c r="S116" t="n">
-        <v>21344367.15</v>
+        <v>22487123.09</v>
       </c>
       <c r="T116" t="n">
         <v>22426358</v>
       </c>
       <c r="U116" t="n">
-        <v>179609.65</v>
+        <v>667014.2</v>
       </c>
       <c r="V116" t="n">
         <v>22426358</v>
@@ -14134,7 +14709,7 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
@@ -14144,7 +14719,12 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14832,7 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
@@ -14262,7 +14842,12 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14955,7 @@
       </c>
       <c r="AD118" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
@@ -14380,7 +14965,12 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14451,7 +15041,7 @@
         <v>364021.94</v>
       </c>
       <c r="R119" t="n">
-        <v>57214.44</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>57214.44</v>
@@ -14460,7 +15050,7 @@
         <v>364021.94</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="V119" t="n">
         <v>2537927</v>
@@ -14488,7 +15078,7 @@
       </c>
       <c r="AD119" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
@@ -14498,7 +15088,12 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14560,13 +15155,13 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>566200</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>988754.48</v>
+        <v>1554954.48</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
@@ -14606,7 +15201,7 @@
       </c>
       <c r="AD120" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
@@ -14616,7 +15211,12 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14724,17 +15324,22 @@
       </c>
       <c r="AD121" t="inlineStr">
         <is>
+          <t>CPM - Equipamentos</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14793,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14842,7 +15447,7 @@
       </c>
       <c r="AD122" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
@@ -14852,7 +15457,12 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -14960,7 +15570,7 @@
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
@@ -14970,7 +15580,12 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15693,7 @@
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
@@ -15088,7 +15703,12 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15816,7 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -15206,7 +15826,12 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15939,7 @@
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
@@ -15324,7 +15949,12 @@
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15432,7 +16062,7 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
@@ -15442,7 +16072,12 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15550,7 +16185,7 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
@@ -15560,7 +16195,12 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15668,7 +16308,7 @@
       </c>
       <c r="AD129" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE129" t="inlineStr">
@@ -15678,7 +16318,12 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15786,7 +16431,7 @@
       </c>
       <c r="AD130" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE130" t="inlineStr">
@@ -15796,7 +16441,12 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -15858,7 +16508,7 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
@@ -15867,13 +16517,13 @@
         <v>525</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T131" t="n">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -15904,17 +16554,22 @@
       </c>
       <c r="AD131" t="inlineStr">
         <is>
+          <t>CPIR - Equipamentos</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
           <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16022,7 +16677,7 @@
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
@@ -16032,7 +16687,12 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16140,7 +16800,7 @@
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
@@ -16150,7 +16810,12 @@
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16258,7 +16923,7 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
@@ -16268,7 +16933,12 @@
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16376,7 +17046,7 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
@@ -16386,7 +17056,12 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16494,7 +17169,7 @@
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
@@ -16504,7 +17179,12 @@
       </c>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16563,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16612,7 +17292,7 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
@@ -16622,7 +17302,12 @@
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16730,7 +17415,7 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
@@ -16740,7 +17425,12 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16848,7 +17538,7 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
@@ -16858,7 +17548,12 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -16908,7 +17603,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>18196243.45</v>
+        <v>24615718.91</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -16920,22 +17615,22 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>18089870.01</v>
+        <v>18810893.01</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>137033545.77</v>
+        <v>142860228.75</v>
       </c>
       <c r="R140" t="n">
-        <v>105921880.08</v>
+        <v>106642903.08</v>
       </c>
       <c r="S140" t="n">
-        <v>108730810.28</v>
+        <v>109451833.28</v>
       </c>
       <c r="T140" t="n">
-        <v>118943675.76</v>
+        <v>124049335.74</v>
       </c>
       <c r="U140" t="n">
         <v>2808930.2</v>
@@ -16966,7 +17661,7 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
@@ -16976,7 +17671,12 @@
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17084,17 +17784,22 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
+          <t>Sesana - Políticas</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>Material de Consumo</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
           <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>Material de Consumo</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17907,7 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic. de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
@@ -17212,7 +17917,12 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17320,7 +18030,7 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
@@ -17330,7 +18040,12 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17380,7 +18095,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2304000</v>
+        <v>2592000</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -17438,7 +18153,7 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
@@ -17448,7 +18163,12 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17556,17 +18276,22 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
+          <t>Sesana - Políticas</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>Contratação PJ com Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
           <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17674,7 +18399,7 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
@@ -17684,7 +18409,12 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17792,7 +18522,7 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
@@ -17802,7 +18532,12 @@
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -17910,7 +18645,7 @@
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Sem detalhamento</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
@@ -17920,7 +18655,12 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>03/02/2026 10:42:17</t>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -18028,17 +18768,22 @@
       </c>
       <c r="AD149" t="inlineStr">
         <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
           <t>Recursos do FUMCAD desvinculados</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>
@@ -18088,7 +18833,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>4254945.75</v>
+        <v>4701260.65</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -18097,7 +18842,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>127680</v>
       </c>
       <c r="O150" t="n">
         <v>3068431.98</v>
@@ -18146,17 +18891,22 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>03/02/2026 10:42:17</t>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>05/02/2026 17:22:33</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>84200</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -902,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>84200</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>50000</v>
+        <v>84200</v>
       </c>
       <c r="W4" t="n">
         <v>50000</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>50000</v>
+        <v>84200</v>
       </c>
       <c r="AA4" t="n">
         <v>5</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2372,10 +2372,10 @@
         <v>17023.38</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5459</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>5459</v>
       </c>
       <c r="T16" t="n">
         <v>7014.46</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4565,16 +4565,16 @@
         </is>
       </c>
       <c r="K34" t="n">
+        <v>1139.21</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1003.1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>16294924</v>
+        <v>16260724</v>
       </c>
       <c r="W43" t="n">
         <v>21072104</v>
@@ -5714,10 +5714,10 @@
         <v>4777180</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="Z43" t="n">
-        <v>21072104</v>
+        <v>21037904</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>1054150.07</v>
+        <v>2092306.37</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>106229.82</v>
+        <v>108749.82</v>
       </c>
       <c r="R117" t="n">
         <v>62133</v>
@@ -14801,7 +14801,7 @@
         <v>63927</v>
       </c>
       <c r="T117" t="n">
-        <v>106229.82</v>
+        <v>108749.82</v>
       </c>
       <c r="U117" t="n">
         <v>1794</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>24615718.91</v>
+        <v>36031507.3</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -17612,7 +17612,7 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>438463.7</v>
       </c>
       <c r="O140" t="n">
         <v>18810893.01</v>
@@ -17621,16 +17621,16 @@
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>142860228.75</v>
+        <v>145589411.7</v>
       </c>
       <c r="R140" t="n">
-        <v>106642903.08</v>
+        <v>109372086.03</v>
       </c>
       <c r="S140" t="n">
-        <v>109451833.28</v>
+        <v>112181016.23</v>
       </c>
       <c r="T140" t="n">
-        <v>124049335.74</v>
+        <v>126778518.69</v>
       </c>
       <c r="U140" t="n">
         <v>2808930.2</v>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2592000</v>
+        <v>2628000</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>
@@ -18833,7 +18833,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>4701260.65</v>
+        <v>6695961.38</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -18842,7 +18842,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>127680</v>
+        <v>964928.4399999999</v>
       </c>
       <c r="O150" t="n">
         <v>3068431.98</v>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>06/02/2026 08:44:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>21963.73</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -773,13 +773,13 @@
         <v>5256476.99</v>
       </c>
       <c r="R3" t="n">
-        <v>4540095.21</v>
+        <v>4944239.18</v>
       </c>
       <c r="S3" t="n">
-        <v>4540095.21</v>
+        <v>4944239.18</v>
       </c>
       <c r="T3" t="n">
-        <v>5256476.99</v>
+        <v>5234513.26</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3877150.67</v>
+        <v>4054651.88</v>
       </c>
       <c r="R10" t="n">
-        <v>87583.42999999999</v>
+        <v>265084.64</v>
       </c>
       <c r="S10" t="n">
-        <v>87583.42999999999</v>
+        <v>265084.64</v>
       </c>
       <c r="T10" t="n">
-        <v>3334162.21</v>
+        <v>3511663.42</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>110.08</v>
+        <v>11940.15</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3848,10 +3848,10 @@
         <v>1687764.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1249842.17</v>
+        <v>1393557.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1311069.24</v>
+        <v>1454784.32</v>
       </c>
       <c r="T28" t="n">
         <v>1485888.62</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>9016.110000000001</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4094,10 +4094,10 @@
         <v>1152411.14</v>
       </c>
       <c r="R30" t="n">
-        <v>998372.9</v>
+        <v>1074180.26</v>
       </c>
       <c r="S30" t="n">
-        <v>1004945.55</v>
+        <v>1080752.91</v>
       </c>
       <c r="T30" t="n">
         <v>1149600.16</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1139.21</v>
+        <v>1204.43</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>5916961.44</v>
       </c>
       <c r="R34" t="n">
-        <v>2981862.7</v>
+        <v>2985047</v>
       </c>
       <c r="S34" t="n">
-        <v>2981862.7</v>
+        <v>2985047</v>
       </c>
       <c r="T34" t="n">
         <v>2985047</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>2034382.45</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10112,13 +10112,13 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>23843.36</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>50000</v>
+        <v>73843.36</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>6926170.67</v>
+        <v>6953424.46</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -12833,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>6926170.67</v>
+        <v>6953424.46</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>483294.93</v>
+        <v>1308418.2</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13319,10 +13319,10 @@
         <v>13728.92</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>13164.1</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>13164.1</v>
       </c>
       <c r="T105" t="n">
         <v>13728.92</v>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14795,10 +14795,10 @@
         <v>108749.82</v>
       </c>
       <c r="R117" t="n">
-        <v>62133</v>
+        <v>64653</v>
       </c>
       <c r="S117" t="n">
-        <v>63927</v>
+        <v>66447</v>
       </c>
       <c r="T117" t="n">
         <v>108749.82</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15164,10 +15164,10 @@
         <v>1554954.48</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>566200</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>566200</v>
       </c>
       <c r="T120" t="n">
         <v>988754.48</v>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>36031507.3</v>
+        <v>39124779.78</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>
@@ -18842,7 +18842,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>964928.4399999999</v>
+        <v>1433738.57</v>
       </c>
       <c r="O150" t="n">
         <v>3068431.98</v>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>06/02/2026 08:44:39</t>
+          <t>07/02/2026 08:30:51</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14672,10 +14672,10 @@
         <v>23851875.51</v>
       </c>
       <c r="R116" t="n">
-        <v>21820108.89</v>
+        <v>21926109.23</v>
       </c>
       <c r="S116" t="n">
-        <v>22487123.09</v>
+        <v>22593123.43</v>
       </c>
       <c r="T116" t="n">
         <v>22426358</v>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>07/02/2026 08:30:51</t>
+          <t>08/02/2026 08:34:40</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>08/02/2026 08:34:40</t>
+          <t>09/02/2026 08:54:09</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG150"/>
+  <dimension ref="A1:AG151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5256476.99</v>
+        <v>5587041.95</v>
       </c>
       <c r="R3" t="n">
         <v>4944239.18</v>
@@ -779,7 +779,7 @@
         <v>4944239.18</v>
       </c>
       <c r="T3" t="n">
-        <v>5234513.26</v>
+        <v>5565078.22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1152411.14</v>
+        <v>1152697.63</v>
       </c>
       <c r="R30" t="n">
         <v>1074180.26</v>
@@ -4100,7 +4100,7 @@
         <v>1080752.91</v>
       </c>
       <c r="T30" t="n">
-        <v>1149600.16</v>
+        <v>1149886.65</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1003.1</v>
+        <v>1204.43</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5444,16 +5444,16 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6558</v>
+        <v>21525.12</v>
       </c>
       <c r="R41" t="n">
-        <v>6558</v>
+        <v>20187</v>
       </c>
       <c r="S41" t="n">
-        <v>10494</v>
+        <v>24123</v>
       </c>
       <c r="T41" t="n">
-        <v>6558</v>
+        <v>21525.12</v>
       </c>
       <c r="U41" t="n">
         <v>3936</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>186346</v>
       </c>
       <c r="Q42" t="n">
         <v>229579.78</v>
@@ -5588,7 +5588,7 @@
         <v>821969</v>
       </c>
       <c r="X42" t="n">
-        <v>186346</v>
+        <v>372692</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5687,31 +5687,31 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>1087620.9</v>
+        <v>1108160.9</v>
       </c>
       <c r="R43" t="n">
-        <v>450875.94</v>
+        <v>651717.9</v>
       </c>
       <c r="S43" t="n">
-        <v>450875.94</v>
+        <v>651717.9</v>
       </c>
       <c r="T43" t="n">
-        <v>1087620.9</v>
+        <v>1108160.9</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>16260724</v>
+        <v>16079724</v>
       </c>
       <c r="W43" t="n">
         <v>21072104</v>
       </c>
       <c r="X43" t="n">
-        <v>4777180</v>
+        <v>5144526</v>
       </c>
       <c r="Y43" t="n">
         <v>34200</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="Q63" t="n">
         <v>627657</v>
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>627657</v>
+        <v>681657</v>
       </c>
       <c r="W63" t="n">
         <v>1226000</v>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11080,11 +11080,11 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2459898.9</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -11102,25 +11102,25 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
@@ -11129,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>5</v>
@@ -11152,12 +11152,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Ricardo Teixeira</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>2459898.9</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -11225,25 +11225,25 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>10919153.01</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>10919153.01</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="W88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AA88" t="n">
         <v>5</v>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11363,10 +11363,10 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="W89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AA89" t="n">
         <v>5</v>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11435,16 +11435,16 @@
         <v>4024</v>
       </c>
       <c r="G90" t="n">
-        <v>4319</v>
+        <v>4318</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11486,19 +11486,19 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="W90" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="X90" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AA90" t="n">
         <v>5</v>
@@ -11506,17 +11506,17 @@
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11567,12 +11567,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11609,19 +11609,19 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="W91" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AA91" t="n">
         <v>5</v>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -11717,34 +11717,34 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="W92" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="X92" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AA92" t="n">
         <v>5</v>
@@ -11762,17 +11762,17 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11804,16 +11804,16 @@
         <v>4024</v>
       </c>
       <c r="G93" t="n">
-        <v>4324</v>
+        <v>4319</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11840,34 +11840,34 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="W93" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="X93" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AA93" t="n">
         <v>5</v>
@@ -11875,17 +11875,17 @@
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -11981,16 +11981,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Y94" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AA94" t="n">
         <v>5</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -12101,19 +12101,19 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Z95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>5</v>
@@ -12136,12 +12136,12 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -12359,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA97" t="n">
         <v>5</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12419,11 +12419,11 @@
         <v>4024</v>
       </c>
       <c r="G98" t="n">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -12443,7 +12443,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W98" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
         <v>0</v>
@@ -12482,7 +12482,7 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA98" t="n">
         <v>5</v>
@@ -12490,12 +12490,12 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -12505,12 +12505,12 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12542,16 +12542,16 @@
         <v>4024</v>
       </c>
       <c r="G99" t="n">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>2092306.37</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -12578,25 +12578,25 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="W99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -12605,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AA99" t="n">
         <v>5</v>
@@ -12613,17 +12613,17 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>2092306.37</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -12701,25 +12701,25 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="W100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AA100" t="n">
         <v>5</v>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>6953424.46</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -12833,16 +12833,16 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>6953424.46</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="W101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -12851,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AA101" t="n">
         <v>5</v>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -12911,16 +12911,16 @@
         <v>4024</v>
       </c>
       <c r="G102" t="n">
-        <v>4332</v>
+        <v>4326</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>1308418.2</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -12947,25 +12947,25 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>5238691</v>
+        <v>6953424.46</v>
       </c>
       <c r="R102" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>8823589.4</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>5238691</v>
+        <v>6953424.46</v>
       </c>
       <c r="U102" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="W102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -12974,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AA102" t="n">
         <v>5</v>
@@ -12982,17 +12982,17 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1308418.2</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -13070,25 +13070,25 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5238691</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>8823589.4</v>
       </c>
       <c r="T103" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="V103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="W103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AA103" t="n">
         <v>5</v>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13157,16 +13157,16 @@
         <v>4024</v>
       </c>
       <c r="G104" t="n">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13193,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -13202,16 +13202,16 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="W104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -13220,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="AA104" t="n">
         <v>5</v>
@@ -13228,17 +13228,17 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13316,25 +13316,25 @@
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>13164.1</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>13164.1</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="W105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="AA105" t="n">
         <v>5</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -13433,31 +13433,31 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>47920</v>
+        <v>13728.92</v>
       </c>
       <c r="R106" t="n">
-        <v>45670</v>
+        <v>13164.1</v>
       </c>
       <c r="S106" t="n">
-        <v>47470</v>
+        <v>13164.1</v>
       </c>
       <c r="T106" t="n">
-        <v>45670</v>
+        <v>13728.92</v>
       </c>
       <c r="U106" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="W106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -13466,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="AA106" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13526,21 +13526,21 @@
         <v>4024</v>
       </c>
       <c r="G107" t="n">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -13556,31 +13556,31 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>47920</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>47470</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="V107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="W107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="AA107" t="n">
         <v>5</v>
@@ -13597,27 +13597,27 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13646,14 +13646,14 @@
         <v>422</v>
       </c>
       <c r="F108" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G108" t="n">
-        <v>2053</v>
+        <v>4335</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>1221823</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -13676,7 +13676,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13685,34 +13685,34 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>4887292</v>
+        <v>50000</v>
       </c>
       <c r="W108" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="X108" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="AA108" t="n">
         <v>5</v>
@@ -13720,12 +13720,12 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13786,11 +13786,11 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>1221823</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13808,34 +13808,34 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="W109" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="X109" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="AA109" t="n">
         <v>5</v>
@@ -13858,12 +13858,12 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -13904,12 +13904,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -13931,34 +13931,34 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="X110" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AA110" t="n">
         <v>5</v>
@@ -13976,17 +13976,17 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14054,34 +14054,34 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>519437</v>
+        <v>150755</v>
       </c>
       <c r="W111" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="X111" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="AA111" t="n">
         <v>5</v>
@@ -14099,7 +14099,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -14171,40 +14171,40 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>139083</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>4701261</v>
+        <v>519437</v>
       </c>
       <c r="W112" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="X112" t="n">
-        <v>251895</v>
+        <v>27832</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="AA112" t="n">
         <v>5</v>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -14294,40 +14294,40 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>282533</v>
+        <v>139083</v>
       </c>
       <c r="R113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="S113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="T113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>282533</v>
+        <v>4701261</v>
       </c>
       <c r="W113" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>251895</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="AA113" t="n">
         <v>5</v>
@@ -14350,12 +14350,12 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14396,12 +14396,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -14423,34 +14423,34 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="W114" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="X114" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="AA114" t="n">
         <v>5</v>
@@ -14468,17 +14468,17 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
         <v>4025</v>
       </c>
       <c r="G115" t="n">
-        <v>4329</v>
+        <v>2053</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14546,34 +14546,34 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>2356400</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="X115" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="AA115" t="n">
         <v>5</v>
@@ -14586,12 +14586,12 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
         <v>4025</v>
       </c>
       <c r="G116" t="n">
-        <v>6178</v>
+        <v>4329</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>333946.2</v>
+        <v>779600</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -14660,43 +14660,43 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="O116" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="R116" t="n">
-        <v>21926109.23</v>
+        <v>1576800</v>
       </c>
       <c r="S116" t="n">
-        <v>22593123.43</v>
+        <v>2356400</v>
       </c>
       <c r="T116" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="U116" t="n">
-        <v>667014.2</v>
+        <v>779600</v>
       </c>
       <c r="V116" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="W116" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Y116" t="n">
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="AA116" t="n">
         <v>5</v>
@@ -14709,12 +14709,12 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>333946.2</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14786,31 +14786,31 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>108749.82</v>
+        <v>23851875.51</v>
       </c>
       <c r="R117" t="n">
-        <v>64653</v>
+        <v>21926109.23</v>
       </c>
       <c r="S117" t="n">
-        <v>66447</v>
+        <v>22593123.43</v>
       </c>
       <c r="T117" t="n">
-        <v>108749.82</v>
+        <v>22426358</v>
       </c>
       <c r="U117" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="V117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="W117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -14819,7 +14819,7 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AA117" t="n">
         <v>5</v>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14915,25 +14915,25 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>88531.96000000001</v>
+        <v>108749.82</v>
       </c>
       <c r="R118" t="n">
-        <v>88531.96000000001</v>
+        <v>64653</v>
       </c>
       <c r="S118" t="n">
-        <v>88531.96000000001</v>
+        <v>66447</v>
       </c>
       <c r="T118" t="n">
-        <v>88531.96000000001</v>
+        <v>108749.82</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="V118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="W118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14942,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AA118" t="n">
         <v>5</v>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15038,25 +15038,25 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>364021.94</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="S119" t="n">
-        <v>57214.44</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="T119" t="n">
-        <v>364021.94</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="U119" t="n">
-        <v>57214.44</v>
+        <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="W119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AA119" t="n">
         <v>5</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>566200</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>1554954.48</v>
+        <v>364021.94</v>
       </c>
       <c r="R120" t="n">
-        <v>566200</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>566200</v>
+        <v>57214.44</v>
       </c>
       <c r="T120" t="n">
-        <v>988754.48</v>
+        <v>364021.94</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="V120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="W120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AA120" t="n">
         <v>5</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -15278,31 +15278,31 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>566200</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>80000</v>
+        <v>1589756.86</v>
       </c>
       <c r="R121" t="n">
-        <v>80000</v>
+        <v>908756.86</v>
       </c>
       <c r="S121" t="n">
-        <v>80000</v>
+        <v>908756.86</v>
       </c>
       <c r="T121" t="n">
-        <v>80000</v>
+        <v>1023556.86</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="W121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AA121" t="n">
         <v>5</v>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15380,16 +15380,16 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>1967.85</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1967.85</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15407,25 +15407,25 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="R122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="S122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="T122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="W122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AA122" t="n">
         <v>5</v>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15494,16 +15494,16 @@
         <v>4025</v>
       </c>
       <c r="G123" t="n">
-        <v>9027</v>
+        <v>6178</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15512,7 +15512,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15530,34 +15530,34 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="W123" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X123" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -15565,17 +15565,17 @@
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15617,7 @@
         <v>4025</v>
       </c>
       <c r="G124" t="n">
-        <v>9030</v>
+        <v>9027</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -15671,16 +15671,16 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA124" t="n">
         <v>5</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15740,7 +15740,7 @@
         <v>4025</v>
       </c>
       <c r="G125" t="n">
-        <v>9044</v>
+        <v>9030</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -15794,16 +15794,16 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA125" t="n">
         <v>5</v>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15860,19 +15860,19 @@
         <v>422</v>
       </c>
       <c r="F126" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G126" t="n">
-        <v>4327</v>
+        <v>9044</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15914,19 +15914,19 @@
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="AA126" t="n">
         <v>5</v>
@@ -15934,17 +15934,17 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         <v>4026</v>
       </c>
       <c r="G127" t="n">
-        <v>4334</v>
+        <v>4327</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -16022,34 +16022,34 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>3469273</v>
+        <v>11949</v>
       </c>
       <c r="W127" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="X127" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AA127" t="n">
         <v>5</v>
@@ -16062,12 +16062,12 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16142,37 +16142,37 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>5374</v>
+        <v>3596273</v>
       </c>
       <c r="W128" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="X128" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AA128" t="n">
         <v>5</v>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -16283,19 +16283,19 @@
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="W129" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="X129" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AA129" t="n">
         <v>5</v>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -16391,7 +16391,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -16400,25 +16400,25 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="W130" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="X130" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AA130" t="n">
         <v>5</v>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -16508,40 +16508,40 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>525</v>
+        <v>4938259.32</v>
       </c>
       <c r="R131" t="n">
-        <v>300</v>
+        <v>469142.51</v>
       </c>
       <c r="S131" t="n">
-        <v>300</v>
+        <v>469142.51</v>
       </c>
       <c r="T131" t="n">
-        <v>300</v>
+        <v>4938259.32</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="W131" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AA131" t="n">
         <v>5</v>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16601,21 +16601,21 @@
         <v>4026</v>
       </c>
       <c r="G132" t="n">
-        <v>9025</v>
+        <v>4334</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -16631,40 +16631,40 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W132" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="X132" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="AA132" t="n">
         <v>5</v>
@@ -16672,27 +16672,27 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16718,22 +16718,22 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F133" t="n">
         <v>4026</v>
       </c>
       <c r="G133" t="n">
-        <v>4322</v>
+        <v>9025</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16775,19 +16775,19 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>7143</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="X133" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="AA133" t="n">
         <v>5</v>
@@ -16795,17 +16795,17 @@
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -16892,25 +16892,25 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>33669</v>
+        <v>7143</v>
       </c>
       <c r="W134" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="X134" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AA134" t="n">
         <v>5</v>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -16970,16 +16970,16 @@
         <v>4026</v>
       </c>
       <c r="G135" t="n">
-        <v>9234</v>
+        <v>4322</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17006,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -17015,25 +17015,25 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="W135" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="X135" t="n">
-        <v>100000</v>
+        <v>187297</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="AA135" t="n">
         <v>5</v>
@@ -17041,17 +17041,17 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17087,22 +17087,22 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F136" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G136" t="n">
-        <v>4426</v>
+        <v>9234</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -17147,16 +17147,16 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="X136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="AA136" t="n">
         <v>5</v>
@@ -17164,17 +17164,17 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -17184,48 +17184,48 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F137" t="n">
         <v>4010</v>
       </c>
       <c r="G137" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>6470104.18</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3235052.09</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -17252,34 +17252,34 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AA137" t="n">
         <v>5</v>
@@ -17292,12 +17292,12 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>6470104.18</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -17366,7 +17366,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17375,34 +17375,34 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="W138" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="X138" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AA138" t="n">
         <v>5</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17452,21 +17452,21 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F139" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G139" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -17513,19 +17513,19 @@
         <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="W139" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AA139" t="n">
         <v>5</v>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17579,13 +17579,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F140" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G140" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>39124779.78</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -17612,43 +17612,43 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>438463.7</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>18810893.01</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>145589411.7</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>109372086.03</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>112181016.23</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>126778518.69</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>2808930.2</v>
+        <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>166077092</v>
+        <v>1000</v>
       </c>
       <c r="W140" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="X140" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="AA140" t="n">
         <v>5</v>
@@ -17661,12 +17661,12 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17717,16 +17717,16 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>39275806.28</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,43 +17735,43 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>438463.7</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>18810893.01</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>146048069.7</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>109372086.03</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>112181016.23</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>127237176.69</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>2808930.2</v>
       </c>
       <c r="V141" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="W141" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AA141" t="n">
         <v>5</v>
@@ -17789,17 +17789,17 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="W142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X142" t="n">
         <v>0</v>
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AA142" t="n">
         <v>5</v>
@@ -17917,12 +17917,12 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -17963,16 +17963,16 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -17984,40 +17984,40 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>52634438.4</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="W143" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="X143" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AA143" t="n">
         <v>5</v>
@@ -18035,17 +18035,17 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2628000</v>
+        <v>5410565.4</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -18107,40 +18107,40 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>180000</v>
+        <v>26317219.2</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>32467200</v>
+        <v>52634438.4</v>
       </c>
       <c r="R144" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="S144" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="T144" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>80849746</v>
+        <v>136889022</v>
       </c>
       <c r="W144" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="X144" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="AA144" t="n">
         <v>5</v>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -18214,11 +18214,11 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>2628000</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18230,40 +18230,40 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>32467200</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>2000</v>
+        <v>80849746</v>
       </c>
       <c r="W145" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Y145" t="n">
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -18286,24 +18286,24 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -18317,27 +18317,27 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F146" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G146" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -18374,10 +18374,10 @@
         <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="W146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -18386,7 +18386,7 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AA146" t="n">
         <v>5</v>
@@ -18394,27 +18394,27 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18497,10 +18497,10 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="W147" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -18563,22 +18563,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F148" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G148" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -18620,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="W148" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -18640,17 +18640,17 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -18686,27 +18686,27 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F149" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G149" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18763,27 +18763,27 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serv. de Tec. da Inf. e Com - PJ</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>09/02/2026 08:54:09</t>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>
@@ -18829,11 +18829,11 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>6695961.38</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -18842,34 +18842,34 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>1433738.57</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>35187195.47</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>31855789.6</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>33468553.7</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>32118763.49</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
         <v>5</v>
@@ -18901,12 +18901,135 @@
       </c>
       <c r="AF150" t="inlineStr">
         <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>10/02/2026 09:01:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>422</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G151" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>6837203.26</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1433738.57</v>
+      </c>
+      <c r="O151" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>35448208.44</v>
+      </c>
+      <c r="R151" t="n">
+        <v>32116802.57</v>
+      </c>
+      <c r="S151" t="n">
+        <v>33729566.67</v>
+      </c>
+      <c r="T151" t="n">
+        <v>32379776.46</v>
+      </c>
+      <c r="U151" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V151" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W151" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>09/02/2026 08:54:09</t>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>10/02/2026 09:01:28</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG150"/>
+  <dimension ref="A1:AG151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -764,22 +764,22 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>21963.73</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5256476.99</v>
+        <v>5587041.95</v>
       </c>
       <c r="R3" t="n">
-        <v>4540095.21</v>
+        <v>4944239.18</v>
       </c>
       <c r="S3" t="n">
-        <v>4540095.21</v>
+        <v>4944239.18</v>
       </c>
       <c r="T3" t="n">
-        <v>5256476.99</v>
+        <v>5565078.22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>84200</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -902,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>84200</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>50000</v>
+        <v>84200</v>
       </c>
       <c r="W4" t="n">
         <v>50000</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>50000</v>
+        <v>84200</v>
       </c>
       <c r="AA4" t="n">
         <v>5</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3877150.67</v>
+        <v>4054651.88</v>
       </c>
       <c r="R10" t="n">
-        <v>87583.42999999999</v>
+        <v>265084.64</v>
       </c>
       <c r="S10" t="n">
-        <v>87583.42999999999</v>
+        <v>265084.64</v>
       </c>
       <c r="T10" t="n">
-        <v>3334162.21</v>
+        <v>3511663.42</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2372,10 +2372,10 @@
         <v>17023.38</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5459</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>5459</v>
       </c>
       <c r="T16" t="n">
         <v>7014.46</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>110.08</v>
+        <v>11940.15</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3848,10 +3848,10 @@
         <v>1687764.06</v>
       </c>
       <c r="R28" t="n">
-        <v>1249842.17</v>
+        <v>1393557.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1311069.24</v>
+        <v>1454784.32</v>
       </c>
       <c r="T28" t="n">
         <v>1485888.62</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>9016.110000000001</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1152411.14</v>
+        <v>1152697.63</v>
       </c>
       <c r="R30" t="n">
-        <v>998372.9</v>
+        <v>1074180.26</v>
       </c>
       <c r="S30" t="n">
-        <v>1004945.55</v>
+        <v>1080752.91</v>
       </c>
       <c r="T30" t="n">
-        <v>1149600.16</v>
+        <v>1149886.65</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1003.1</v>
+        <v>1204.43</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1204.43</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4586,10 +4586,10 @@
         <v>5916961.44</v>
       </c>
       <c r="R34" t="n">
-        <v>2981862.7</v>
+        <v>2985047</v>
       </c>
       <c r="S34" t="n">
-        <v>2981862.7</v>
+        <v>2985047</v>
       </c>
       <c r="T34" t="n">
         <v>2985047</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5444,16 +5444,16 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6558</v>
+        <v>21525.12</v>
       </c>
       <c r="R41" t="n">
-        <v>6558</v>
+        <v>20187</v>
       </c>
       <c r="S41" t="n">
-        <v>10494</v>
+        <v>24123</v>
       </c>
       <c r="T41" t="n">
-        <v>6558</v>
+        <v>21525.12</v>
       </c>
       <c r="U41" t="n">
         <v>3936</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>186346</v>
       </c>
       <c r="Q42" t="n">
         <v>229579.78</v>
@@ -5588,7 +5588,7 @@
         <v>821969</v>
       </c>
       <c r="X42" t="n">
-        <v>186346</v>
+        <v>372692</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5687,37 +5687,37 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>1087620.9</v>
+        <v>1108160.9</v>
       </c>
       <c r="R43" t="n">
-        <v>450875.94</v>
+        <v>651717.9</v>
       </c>
       <c r="S43" t="n">
-        <v>450875.94</v>
+        <v>651717.9</v>
       </c>
       <c r="T43" t="n">
-        <v>1087620.9</v>
+        <v>1108160.9</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>16294924</v>
+        <v>16079724</v>
       </c>
       <c r="W43" t="n">
         <v>21072104</v>
       </c>
       <c r="X43" t="n">
-        <v>4777180</v>
+        <v>5144526</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="Z43" t="n">
-        <v>21072104</v>
+        <v>21037904</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>2034382.45</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="Q63" t="n">
         <v>627657</v>
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>627657</v>
+        <v>681657</v>
       </c>
       <c r="W63" t="n">
         <v>1226000</v>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10112,13 +10112,13 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>23843.36</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>50000</v>
+        <v>73843.36</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11080,11 +11080,11 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2459898.9</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -11102,25 +11102,25 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>2861229.41</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>10919153.01</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
@@ -11129,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>12675633</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>5</v>
@@ -11152,12 +11152,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Emendas Parlamentares - Ricardo Teixeira</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>2459898.9</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -11225,25 +11225,25 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>10919153.01</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2861229.41</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>10919153.01</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="W88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="X88" t="n">
         <v>0</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>50000</v>
+        <v>12675633</v>
       </c>
       <c r="AA88" t="n">
         <v>5</v>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11363,10 +11363,10 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="W89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -11375,7 +11375,7 @@
         <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>378632</v>
+        <v>50000</v>
       </c>
       <c r="AA89" t="n">
         <v>5</v>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11435,16 +11435,16 @@
         <v>4024</v>
       </c>
       <c r="G90" t="n">
-        <v>4319</v>
+        <v>4318</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>33804100</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11486,19 +11486,19 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>8373</v>
+        <v>378632</v>
       </c>
       <c r="W90" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="X90" t="n">
-        <v>2225</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>10598</v>
+        <v>378632</v>
       </c>
       <c r="AA90" t="n">
         <v>5</v>
@@ -11506,17 +11506,17 @@
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>CPLGBTI - Políticas</t>
+          <t>CPJ</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>Taxa Rainbow</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11567,12 +11567,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33804100</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11609,19 +11609,19 @@
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>4000</v>
+        <v>8373</v>
       </c>
       <c r="W91" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2225</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>4000</v>
+        <v>10598</v>
       </c>
       <c r="AA91" t="n">
         <v>5</v>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Taxa Rainbow</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11690,12 +11690,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -11717,34 +11717,34 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>4551281.7</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>9813947</v>
+        <v>4000</v>
       </c>
       <c r="W92" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="X92" t="n">
-        <v>2607835</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>12421782</v>
+        <v>4000</v>
       </c>
       <c r="AA92" t="n">
         <v>5</v>
@@ -11762,17 +11762,17 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11804,16 +11804,16 @@
         <v>4024</v>
       </c>
       <c r="G93" t="n">
-        <v>4324</v>
+        <v>4319</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>CPIPTD</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11840,34 +11840,34 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>4551281.7</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>9813947</v>
       </c>
       <c r="W93" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="X93" t="n">
-        <v>56000</v>
+        <v>2607835</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>56000</v>
+        <v>12421782</v>
       </c>
       <c r="AA93" t="n">
         <v>5</v>
@@ -11875,17 +11875,17 @@
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Imigrantes</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>CPIPTD - Políticas</t>
+          <t>CPLGBTI - Políticas</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -11981,16 +11981,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="Y94" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AA94" t="n">
         <v>5</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -12101,19 +12101,19 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Z95" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>5</v>
@@ -12136,12 +12136,12 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
+          <t>Recursos destinados ao Orçamento Cidadão</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB IQ</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12310,7 +12310,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -12359,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="AA97" t="n">
         <v>5</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB SM</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12419,11 +12419,11 @@
         <v>4024</v>
       </c>
       <c r="G98" t="n">
-        <v>4325</v>
+        <v>4324</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12433,7 +12433,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -12443,7 +12443,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W98" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
         <v>0</v>
@@ -12482,7 +12482,7 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="AA98" t="n">
         <v>5</v>
@@ -12490,12 +12490,12 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Drogas</t>
+          <t>Imigrantes</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPIPTD - Políticas</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -12505,12 +12505,12 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao Orçamento Cidadão - SUB CT</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12542,16 +12542,16 @@
         <v>4024</v>
       </c>
       <c r="G99" t="n">
-        <v>4326</v>
+        <v>4325</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>CPLGBTI</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>1054150.07</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -12578,25 +12578,25 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>10052704</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="W99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="X99" t="n">
         <v>0</v>
@@ -12605,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>10052704</v>
+        <v>1000</v>
       </c>
       <c r="AA99" t="n">
         <v>5</v>
@@ -12613,17 +12613,17 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>LGBTI</t>
+          <t>Drogas</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>CPLGBTI - Equipamentos</t>
+          <t>CPD</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>2092306.37</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -12701,25 +12701,25 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>10052704</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="W100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
@@ -12728,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>100000</v>
+        <v>10052704</v>
       </c>
       <c r="AA100" t="n">
         <v>5</v>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -12833,16 +12833,16 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>6926170.67</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="W101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
@@ -12851,7 +12851,7 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>8429440</v>
+        <v>100000</v>
       </c>
       <c r="AA101" t="n">
         <v>5</v>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -12911,16 +12911,16 @@
         <v>4024</v>
       </c>
       <c r="G102" t="n">
-        <v>4332</v>
+        <v>4326</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12929,7 +12929,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>483294.93</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -12947,25 +12947,25 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>5238691</v>
+        <v>6953424.46</v>
       </c>
       <c r="R102" t="n">
-        <v>5238691</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>8823589.4</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>5238691</v>
+        <v>6953424.46</v>
       </c>
       <c r="U102" t="n">
-        <v>3584898.4</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="W102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="X102" t="n">
         <v>0</v>
@@ -12974,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>5238691</v>
+        <v>8429440</v>
       </c>
       <c r="AA102" t="n">
         <v>5</v>
@@ -12982,17 +12982,17 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>LGBTI</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>CPLGBTI - Equipamentos</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13052,7 +13052,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1308418.2</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -13070,25 +13070,25 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5238691</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>8823589.4</v>
       </c>
       <c r="T103" t="n">
-        <v>240000</v>
+        <v>5238691</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>3584898.4</v>
       </c>
       <c r="V103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="W103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="X103" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
         <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>867556</v>
+        <v>5238691</v>
       </c>
       <c r="AA103" t="n">
         <v>5</v>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13157,16 +13157,16 @@
         <v>4024</v>
       </c>
       <c r="G104" t="n">
-        <v>4333</v>
+        <v>4332</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13193,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -13202,16 +13202,16 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="W104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="X104" t="n">
         <v>0</v>
@@ -13220,7 +13220,7 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>321493</v>
+        <v>867556</v>
       </c>
       <c r="AA104" t="n">
         <v>5</v>
@@ -13228,17 +13228,17 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Centro Público</t>
+          <t>Ouvidoria</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>CPDDH</t>
+          <t>ODH</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13316,7 +13316,7 @@
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -13325,16 +13325,16 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>13728.92</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="W105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="X105" t="n">
         <v>0</v>
@@ -13343,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>237085</v>
+        <v>321493</v>
       </c>
       <c r="AA105" t="n">
         <v>5</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -13433,31 +13433,31 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>47920</v>
+        <v>13728.92</v>
       </c>
       <c r="R106" t="n">
-        <v>45670</v>
+        <v>13164.1</v>
       </c>
       <c r="S106" t="n">
-        <v>47470</v>
+        <v>13164.1</v>
       </c>
       <c r="T106" t="n">
-        <v>45670</v>
+        <v>13728.92</v>
       </c>
       <c r="U106" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="W106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="X106" t="n">
         <v>0</v>
@@ -13466,7 +13466,7 @@
         <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>45670</v>
+        <v>237085</v>
       </c>
       <c r="AA106" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13526,21 +13526,21 @@
         <v>4024</v>
       </c>
       <c r="G107" t="n">
-        <v>4335</v>
+        <v>4333</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -13556,31 +13556,31 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>47920</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>47470</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>45670</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="V107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="W107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>50000</v>
+        <v>45670</v>
       </c>
       <c r="AA107" t="n">
         <v>5</v>
@@ -13597,27 +13597,27 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>Centro Público</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPDDH</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13646,14 +13646,14 @@
         <v>422</v>
       </c>
       <c r="F108" t="n">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="G108" t="n">
-        <v>2053</v>
+        <v>4335</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>1221823</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -13676,7 +13676,7 @@
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>814548.67</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13685,34 +13685,34 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>4887292</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>4887292</v>
+        <v>50000</v>
       </c>
       <c r="W108" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="X108" t="n">
-        <v>261863</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>5149155</v>
+        <v>50000</v>
       </c>
       <c r="AA108" t="n">
         <v>5</v>
@@ -13720,12 +13720,12 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>Egressos</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13786,11 +13786,11 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>1221823</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>814548.67</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13808,34 +13808,34 @@
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="T109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>0</v>
+        <v>4887292</v>
       </c>
       <c r="W109" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="X109" t="n">
-        <v>2000</v>
+        <v>261863</v>
       </c>
       <c r="Y109" t="n">
         <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2000</v>
+        <v>5149155</v>
       </c>
       <c r="AA109" t="n">
         <v>5</v>
@@ -13858,12 +13858,12 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>Código Genérico</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -13904,12 +13904,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -13931,34 +13931,34 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>11808</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>150755</v>
+        <v>0</v>
       </c>
       <c r="W110" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="X110" t="n">
-        <v>8077</v>
+        <v>2000</v>
       </c>
       <c r="Y110" t="n">
         <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>158832</v>
+        <v>2000</v>
       </c>
       <c r="AA110" t="n">
         <v>5</v>
@@ -13976,17 +13976,17 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14054,34 +14054,34 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>11808</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>519437</v>
+        <v>150755</v>
       </c>
       <c r="W111" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="X111" t="n">
-        <v>27832</v>
+        <v>8077</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>547269</v>
+        <v>158832</v>
       </c>
       <c r="AA111" t="n">
         <v>5</v>
@@ -14099,7 +14099,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -14171,40 +14171,40 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>139083</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>136419</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>4701261</v>
+        <v>519437</v>
       </c>
       <c r="W112" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="X112" t="n">
-        <v>251895</v>
+        <v>27832</v>
       </c>
       <c r="Y112" t="n">
         <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>4953156</v>
+        <v>547269</v>
       </c>
       <c r="AA112" t="n">
         <v>5</v>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -14294,40 +14294,40 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>2664</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>282533</v>
+        <v>139083</v>
       </c>
       <c r="R113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="S113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="T113" t="n">
-        <v>282533</v>
+        <v>136419</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>282533</v>
+        <v>4701261</v>
       </c>
       <c r="W113" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>251895</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>282533</v>
+        <v>4953156</v>
       </c>
       <c r="AA113" t="n">
         <v>5</v>
@@ -14350,12 +14350,12 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14396,12 +14396,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -14423,34 +14423,34 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>282533</v>
       </c>
       <c r="W114" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="X114" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>10000</v>
+        <v>282533</v>
       </c>
       <c r="AA114" t="n">
         <v>5</v>
@@ -14468,17 +14468,17 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
         <v>4025</v>
       </c>
       <c r="G115" t="n">
-        <v>4329</v>
+        <v>2053</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14546,34 +14546,34 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
-        <v>2356400</v>
+        <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="X115" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="AA115" t="n">
         <v>5</v>
@@ -14586,12 +14586,12 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - CMB</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
         <v>4025</v>
       </c>
       <c r="G116" t="n">
-        <v>6178</v>
+        <v>4329</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>333946.2</v>
+        <v>779600</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -14660,43 +14660,43 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>779600</v>
       </c>
       <c r="O116" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="R116" t="n">
-        <v>21820108.89</v>
+        <v>1576800</v>
       </c>
       <c r="S116" t="n">
-        <v>22487123.09</v>
+        <v>2356400</v>
       </c>
       <c r="T116" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="U116" t="n">
-        <v>667014.2</v>
+        <v>779600</v>
       </c>
       <c r="V116" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="W116" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Y116" t="n">
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="AA116" t="n">
         <v>5</v>
@@ -14709,12 +14709,12 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>333946.2</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14786,31 +14786,31 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>106229.82</v>
+        <v>23851875.51</v>
       </c>
       <c r="R117" t="n">
-        <v>62133</v>
+        <v>21926109.23</v>
       </c>
       <c r="S117" t="n">
-        <v>63927</v>
+        <v>22593123.43</v>
       </c>
       <c r="T117" t="n">
-        <v>106229.82</v>
+        <v>22426358</v>
       </c>
       <c r="U117" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="V117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="W117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -14819,7 +14819,7 @@
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AA117" t="n">
         <v>5</v>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14915,25 +14915,25 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>88531.96000000001</v>
+        <v>108749.82</v>
       </c>
       <c r="R118" t="n">
-        <v>88531.96000000001</v>
+        <v>64653</v>
       </c>
       <c r="S118" t="n">
-        <v>88531.96000000001</v>
+        <v>66447</v>
       </c>
       <c r="T118" t="n">
-        <v>88531.96000000001</v>
+        <v>108749.82</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="V118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="W118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14942,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AA118" t="n">
         <v>5</v>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15038,25 +15038,25 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>364021.94</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="S119" t="n">
-        <v>57214.44</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="T119" t="n">
-        <v>364021.94</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="U119" t="n">
-        <v>57214.44</v>
+        <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="W119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AA119" t="n">
         <v>5</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>566200</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>1554954.48</v>
+        <v>364021.94</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="T120" t="n">
-        <v>988754.48</v>
+        <v>364021.94</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="V120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="W120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AA120" t="n">
         <v>5</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -15278,31 +15278,31 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>566200</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>80000</v>
+        <v>1589756.86</v>
       </c>
       <c r="R121" t="n">
-        <v>80000</v>
+        <v>908756.86</v>
       </c>
       <c r="S121" t="n">
-        <v>80000</v>
+        <v>908756.86</v>
       </c>
       <c r="T121" t="n">
-        <v>80000</v>
+        <v>1023556.86</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="W121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AA121" t="n">
         <v>5</v>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15380,16 +15380,16 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>1967.85</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1967.85</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15407,25 +15407,25 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="R122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="S122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="T122" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="W122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AA122" t="n">
         <v>5</v>
@@ -15452,17 +15452,17 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15494,16 +15494,16 @@
         <v>4025</v>
       </c>
       <c r="G123" t="n">
-        <v>9027</v>
+        <v>6178</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15512,7 +15512,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15530,34 +15530,34 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="W123" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X123" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="n">
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -15565,17 +15565,17 @@
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15617,7 @@
         <v>4025</v>
       </c>
       <c r="G124" t="n">
-        <v>9030</v>
+        <v>9027</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -15671,16 +15671,16 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA124" t="n">
         <v>5</v>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15740,7 +15740,7 @@
         <v>4025</v>
       </c>
       <c r="G125" t="n">
-        <v>9044</v>
+        <v>9030</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -15794,16 +15794,16 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA125" t="n">
         <v>5</v>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15860,19 +15860,19 @@
         <v>422</v>
       </c>
       <c r="F126" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G126" t="n">
-        <v>4327</v>
+        <v>9044</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -15914,19 +15914,19 @@
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="AA126" t="n">
         <v>5</v>
@@ -15934,17 +15934,17 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         <v>4026</v>
       </c>
       <c r="G127" t="n">
-        <v>4334</v>
+        <v>4327</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -16022,34 +16022,34 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>3469273</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>3469273</v>
+        <v>11949</v>
       </c>
       <c r="W127" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="X127" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AA127" t="n">
         <v>5</v>
@@ -16062,12 +16062,12 @@
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16142,37 +16142,37 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>3469273</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>5374</v>
+        <v>3596273</v>
       </c>
       <c r="W128" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="X128" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AA128" t="n">
         <v>5</v>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -16283,19 +16283,19 @@
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="W129" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="X129" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AA129" t="n">
         <v>5</v>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -16391,7 +16391,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -16400,25 +16400,25 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>4890595.9</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="W130" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="X130" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AA130" t="n">
         <v>5</v>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16492,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -16508,40 +16508,40 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>525</v>
+        <v>4938259.32</v>
       </c>
       <c r="R131" t="n">
-        <v>300</v>
+        <v>469142.51</v>
       </c>
       <c r="S131" t="n">
-        <v>300</v>
+        <v>469142.51</v>
       </c>
       <c r="T131" t="n">
-        <v>300</v>
+        <v>4938259.32</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="W131" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AA131" t="n">
         <v>5</v>
@@ -16564,12 +16564,12 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16601,21 +16601,21 @@
         <v>4026</v>
       </c>
       <c r="G132" t="n">
-        <v>9025</v>
+        <v>4334</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -16631,40 +16631,40 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S132" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W132" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="X132" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="AA132" t="n">
         <v>5</v>
@@ -16672,27 +16672,27 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16718,22 +16718,22 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F133" t="n">
         <v>4026</v>
       </c>
       <c r="G133" t="n">
-        <v>4322</v>
+        <v>9025</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -16775,19 +16775,19 @@
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>7143</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="X133" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="AA133" t="n">
         <v>5</v>
@@ -16795,17 +16795,17 @@
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0</v>
@@ -16892,25 +16892,25 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>33669</v>
+        <v>7143</v>
       </c>
       <c r="W134" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="X134" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AA134" t="n">
         <v>5</v>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -16970,16 +16970,16 @@
         <v>4026</v>
       </c>
       <c r="G135" t="n">
-        <v>9234</v>
+        <v>4322</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17006,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -17015,25 +17015,25 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="W135" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="X135" t="n">
-        <v>100000</v>
+        <v>187297</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="AA135" t="n">
         <v>5</v>
@@ -17041,17 +17041,17 @@
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17073,12 +17073,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17087,22 +17087,22 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F136" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G136" t="n">
-        <v>4426</v>
+        <v>9234</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -17147,16 +17147,16 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="X136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="AA136" t="n">
         <v>5</v>
@@ -17164,17 +17164,17 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -17184,48 +17184,48 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F137" t="n">
         <v>4010</v>
       </c>
       <c r="G137" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -17234,7 +17234,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>6470104.18</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3235052.09</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -17252,34 +17252,34 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AA137" t="n">
         <v>5</v>
@@ -17292,12 +17292,12 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>6470104.18</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -17366,7 +17366,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3235052.09</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17375,34 +17375,34 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="W138" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="X138" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AA138" t="n">
         <v>5</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17452,21 +17452,21 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F139" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G139" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -17513,19 +17513,19 @@
         <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="W139" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AA139" t="n">
         <v>5</v>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="AD139" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE139" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17579,13 +17579,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F140" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G140" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>24615718.91</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -17615,40 +17615,40 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>18810893.01</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>142860228.75</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>106642903.08</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>109451833.28</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>124049335.74</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>2808930.2</v>
+        <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>166077092</v>
+        <v>1000</v>
       </c>
       <c r="W140" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="X140" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="AA140" t="n">
         <v>5</v>
@@ -17661,12 +17661,12 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17717,16 +17717,16 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>39275806.28</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,43 +17735,43 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>438463.7</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>18810893.01</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>146048069.7</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>109372086.03</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>112181016.23</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>127237176.69</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>2808930.2</v>
       </c>
       <c r="V141" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="W141" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AA141" t="n">
         <v>5</v>
@@ -17789,17 +17789,17 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="V142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="W142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X142" t="n">
         <v>0</v>
@@ -17894,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AA142" t="n">
         <v>5</v>
@@ -17917,12 +17917,12 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -17963,16 +17963,16 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="K143" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -17984,40 +17984,40 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>52634438.4</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>26317219.2</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="W143" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="X143" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AA143" t="n">
         <v>5</v>
@@ -18035,17 +18035,17 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2592000</v>
+        <v>5410565.4</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -18107,40 +18107,40 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>180000</v>
+        <v>26317219.2</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>32467200</v>
+        <v>52634438.4</v>
       </c>
       <c r="R144" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="S144" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="T144" t="n">
-        <v>32287200</v>
+        <v>26317219.2</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>80849746</v>
+        <v>136889022</v>
       </c>
       <c r="W144" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="X144" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="AA144" t="n">
         <v>5</v>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -18214,11 +18214,11 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>2628000</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18230,40 +18230,40 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>180000</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>32467200</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="S145" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>32287200</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>2000</v>
+        <v>80849746</v>
       </c>
       <c r="W145" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Y145" t="n">
         <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -18286,24 +18286,24 @@
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -18317,27 +18317,27 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F146" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G146" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -18374,10 +18374,10 @@
         <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="W146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="X146" t="n">
         <v>0</v>
@@ -18386,7 +18386,7 @@
         <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AA146" t="n">
         <v>5</v>
@@ -18394,27 +18394,27 @@
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18497,10 +18497,10 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="W147" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -18563,22 +18563,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F148" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G148" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -18620,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="W148" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -18640,17 +18640,17 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -18686,27 +18686,27 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F149" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G149" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18763,27 +18763,27 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serv. de Tec. da Inf. e Com - PJ</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>05/02/2026 17:22:33</t>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>
@@ -18829,11 +18829,11 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="K150" t="n">
-        <v>4701260.65</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -18842,34 +18842,34 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>127680</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>35187195.47</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>31855789.6</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
-        <v>33468553.7</v>
+        <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>32118763.49</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="W150" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
         <v>5</v>
@@ -18901,12 +18901,135 @@
       </c>
       <c r="AF150" t="inlineStr">
         <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>10/02/2026 14:20:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>422</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G151" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>6837203.26</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1433738.57</v>
+      </c>
+      <c r="O151" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>35448208.44</v>
+      </c>
+      <c r="R151" t="n">
+        <v>32116802.57</v>
+      </c>
+      <c r="S151" t="n">
+        <v>33729566.67</v>
+      </c>
+      <c r="T151" t="n">
+        <v>32379776.46</v>
+      </c>
+      <c r="U151" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V151" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W151" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>05/02/2026 17:22:33</t>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>10/02/2026 14:20:16</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG151"/>
+  <dimension ref="A1:AG152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>156517.68</v>
       </c>
       <c r="O3" t="n">
         <v>21963.73</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>11257.26</v>
       </c>
       <c r="O8" t="n">
         <v>140000</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1625,25 +1625,25 @@
         <v>12545</v>
       </c>
       <c r="O10" t="n">
-        <v>542988.46</v>
+        <v>543015.46</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4054651.88</v>
+        <v>4103046.13</v>
       </c>
       <c r="R10" t="n">
-        <v>265084.64</v>
+        <v>312599.25</v>
       </c>
       <c r="S10" t="n">
-        <v>265084.64</v>
+        <v>314619.89</v>
       </c>
       <c r="T10" t="n">
-        <v>3511663.42</v>
+        <v>3560030.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2020.64</v>
       </c>
       <c r="V10" t="n">
         <v>12568415</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4214,16 +4214,16 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>480000</v>
+        <v>860517</v>
       </c>
       <c r="R31" t="n">
-        <v>480000</v>
+        <v>848517</v>
       </c>
       <c r="S31" t="n">
-        <v>480000</v>
+        <v>848517</v>
       </c>
       <c r="T31" t="n">
-        <v>480000</v>
+        <v>860517</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5663.52</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>761377.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>245581.64</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1054150.07</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>333946.2</v>
+        <v>610967.48</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3235052.09</v>
+        <v>6470104.18</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>39275806.28</v>
+        <v>39279306.28</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>438463.7</v>
+        <v>18196243.45</v>
       </c>
       <c r="O141" t="n">
         <v>18810893.01</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2304000</v>
       </c>
       <c r="O145" t="n">
         <v>180000</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18414,19 +18414,19 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -18440,22 +18440,22 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F147" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G147" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -18497,10 +18497,10 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W147" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -18517,17 +18517,17 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Sesana - Políticas</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -18620,10 +18620,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="W148" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18686,22 +18686,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F149" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G149" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="W149" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18763,17 +18763,17 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18809,27 +18809,27 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F150" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G150" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -18866,10 +18866,10 @@
         <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W150" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA150" t="n">
         <v>5</v>
@@ -18886,27 +18886,27 @@
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serv. de Tec. da Inf. e Com - PJ</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>10/02/2026 14:20:16</t>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>
@@ -18952,11 +18952,11 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="K151" t="n">
-        <v>6837203.26</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -18965,34 +18965,34 @@
         <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>1433738.57</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>35448208.44</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>32116802.57</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
-        <v>33729566.67</v>
+        <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>32379776.46</v>
+        <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V151" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X151" t="n">
         <v>0</v>
@@ -19001,7 +19001,7 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AA151" t="n">
         <v>5</v>
@@ -19024,12 +19024,135 @@
       </c>
       <c r="AF151" t="inlineStr">
         <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>11/02/2026 08:54:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>422</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G152" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>6837203.26</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>4254945.75</v>
+      </c>
+      <c r="O152" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>35448208.44</v>
+      </c>
+      <c r="R152" t="n">
+        <v>32116802.57</v>
+      </c>
+      <c r="S152" t="n">
+        <v>33729566.67</v>
+      </c>
+      <c r="T152" t="n">
+        <v>32379776.46</v>
+      </c>
+      <c r="U152" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V152" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W152" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>10/02/2026 14:20:16</t>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>11/02/2026 08:54:51</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>264605.68</v>
+        <v>505273.57</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>12545</v>
+        <v>190046.21</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4103046.13</v>
+        <v>4113088.73</v>
       </c>
       <c r="R10" t="n">
         <v>312599.25</v>
@@ -1640,7 +1640,7 @@
         <v>314619.89</v>
       </c>
       <c r="T10" t="n">
-        <v>3560030.67</v>
+        <v>3570073.27</v>
       </c>
       <c r="U10" t="n">
         <v>2020.64</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>124658.62</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>11940.15</v>
+        <v>106308.87</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1687764.06</v>
+        <v>1752650.4</v>
       </c>
       <c r="R28" t="n">
         <v>1393557.25</v>
@@ -3854,7 +3854,7 @@
         <v>1454784.32</v>
       </c>
       <c r="T28" t="n">
-        <v>1485888.62</v>
+        <v>1550774.96</v>
       </c>
       <c r="U28" t="n">
         <v>61227.07</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9016.110000000001</v>
+        <v>30748.68</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1152697.63</v>
+        <v>1152966.81</v>
       </c>
       <c r="R30" t="n">
         <v>1074180.26</v>
@@ -4100,7 +4100,7 @@
         <v>1080752.91</v>
       </c>
       <c r="T30" t="n">
-        <v>1149886.65</v>
+        <v>1150155.83</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1204.43</v>
+        <v>1854.36</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>5663.52</v>
+        <v>31441.75</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>122450</v>
+        <v>244900</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>814548.67</v>
+        <v>1221823</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>779600</v>
+        <v>1576800</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>610967.48</v>
+        <v>3646287.13</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14783,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>333946.2</v>
       </c>
       <c r="O117" t="n">
         <v>1425517.51</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>39279306.28</v>
+        <v>39827097.78</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,16 +17735,16 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>18196243.45</v>
+        <v>28779995.28</v>
       </c>
       <c r="O141" t="n">
-        <v>18810893.01</v>
+        <v>19269551.01</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>146048069.7</v>
+        <v>147777170.7</v>
       </c>
       <c r="R141" t="n">
         <v>109372086.03</v>
@@ -17753,7 +17753,7 @@
         <v>112181016.23</v>
       </c>
       <c r="T141" t="n">
-        <v>127237176.69</v>
+        <v>128507619.69</v>
       </c>
       <c r="U141" t="n">
         <v>2808930.2</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2304000</v>
+        <v>2592000</v>
       </c>
       <c r="O145" t="n">
         <v>180000</v>
@@ -18236,7 +18236,7 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>32467200</v>
+        <v>32473650</v>
       </c>
       <c r="R145" t="n">
         <v>32287200</v>
@@ -18245,7 +18245,7 @@
         <v>32287200</v>
       </c>
       <c r="T145" t="n">
-        <v>32287200</v>
+        <v>32293650</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>6837203.26</v>
+        <v>7720620.16</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>11/02/2026 08:54:51</t>
+          <t>12/02/2026 07:07:43</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>12/02/2026 07:07:43</t>
+          <t>12/02/2026 11:11:08</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>12/02/2026 11:11:08</t>
+          <t>12/02/2026 12:44:54</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>505273.57</v>
+        <v>535673.5699999999</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>156517.68</v>
+        <v>264605.68</v>
       </c>
       <c r="O3" t="n">
         <v>21963.73</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4113088.73</v>
+        <v>4151610.99</v>
       </c>
       <c r="R10" t="n">
-        <v>312599.25</v>
+        <v>351121.51</v>
       </c>
       <c r="S10" t="n">
-        <v>314619.89</v>
+        <v>353142.15</v>
       </c>
       <c r="T10" t="n">
-        <v>3570073.27</v>
+        <v>3608595.53</v>
       </c>
       <c r="U10" t="n">
         <v>2020.64</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>106308.87</v>
+        <v>149384.58</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>110.08</v>
       </c>
       <c r="O28" t="n">
         <v>201875.44</v>
@@ -3845,19 +3845,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1752650.4</v>
+        <v>2034431.44</v>
       </c>
       <c r="R28" t="n">
         <v>1393557.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1454784.32</v>
+        <v>1505940.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1550774.96</v>
+        <v>1832556</v>
       </c>
       <c r="U28" t="n">
-        <v>61227.07</v>
+        <v>112383.13</v>
       </c>
       <c r="V28" t="n">
         <v>1832556</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>30748.68</v>
+        <v>40624.92</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1854.36</v>
+        <v>5192.79</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1204.43</v>
+        <v>1522.86</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8150,16 +8150,16 @@
         <v>54000</v>
       </c>
       <c r="Q63" t="n">
-        <v>627657</v>
+        <v>680791.95</v>
       </c>
       <c r="R63" t="n">
-        <v>627657</v>
+        <v>680791.95</v>
       </c>
       <c r="S63" t="n">
-        <v>627657</v>
+        <v>680791.95</v>
       </c>
       <c r="T63" t="n">
-        <v>627657</v>
+        <v>680791.95</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11207,16 +11207,16 @@
         </is>
       </c>
       <c r="K88" t="n">
+        <v>2861229.41</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
         <v>2459898.9</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13061,7 +13061,7 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1308418.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14036,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14300,16 +14300,16 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>139083</v>
+        <v>354272.62</v>
       </c>
       <c r="R113" t="n">
-        <v>136419</v>
+        <v>351608.62</v>
       </c>
       <c r="S113" t="n">
-        <v>136419</v>
+        <v>351608.62</v>
       </c>
       <c r="T113" t="n">
-        <v>136419</v>
+        <v>351608.62</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>3646287.13</v>
+        <v>4682693.05</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>11112.8</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16145,16 +16145,16 @@
         <v>127000</v>
       </c>
       <c r="Q128" t="n">
-        <v>3469273</v>
+        <v>3595409.87</v>
       </c>
       <c r="R128" t="n">
-        <v>3469273</v>
+        <v>3595409.87</v>
       </c>
       <c r="S128" t="n">
-        <v>3469273</v>
+        <v>3595409.87</v>
       </c>
       <c r="T128" t="n">
-        <v>3469273</v>
+        <v>3595409.87</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>39827097.78</v>
+        <v>40640152.52</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>28779995.28</v>
+        <v>35663951.76</v>
       </c>
       <c r="O141" t="n">
         <v>19269551.01</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2949590.4</v>
       </c>
       <c r="O144" t="n">
         <v>26317219.2</v>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>2628000</v>
+        <v>2664000</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>7720620.16</v>
+        <v>9072713.01</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19088,7 +19088,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>4254945.75</v>
+        <v>4701260.65</v>
       </c>
       <c r="O152" t="n">
         <v>3068431.98</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>12/02/2026 12:44:54</t>
+          <t>13/02/2026 07:41:46</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="R6" t="n">
         <v>4984</v>
@@ -1148,7 +1148,7 @@
         <v>4984</v>
       </c>
       <c r="T6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>190046.21</v>
+        <v>194146.21</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4151610.99</v>
+        <v>11571411.55</v>
       </c>
       <c r="R10" t="n">
-        <v>351121.51</v>
+        <v>4825017.69</v>
       </c>
       <c r="S10" t="n">
-        <v>353142.15</v>
+        <v>4827038.33</v>
       </c>
       <c r="T10" t="n">
-        <v>3608595.53</v>
+        <v>11028396.09</v>
       </c>
       <c r="U10" t="n">
         <v>2020.64</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC - Manutenção</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Tecnologia - Comunicação</t>
+          <t>DTIC - Comunicação</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>Tecnologia - Comunicação</t>
+          <t>DTIC - Comunicação</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Tecnologia - Comunicação</t>
+          <t>DTIC - Comunicação</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>149384.58</v>
+        <v>157713.7</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>201875.44</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>9180</v>
       </c>
       <c r="Q28" t="n">
         <v>2034431.44</v>
@@ -3860,7 +3860,7 @@
         <v>112383.13</v>
       </c>
       <c r="V28" t="n">
-        <v>1832556</v>
+        <v>1841736</v>
       </c>
       <c r="W28" t="n">
         <v>1841736</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4091,28 +4091,28 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1152966.81</v>
+        <v>1516933.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1074180.26</v>
+        <v>1513567.3</v>
       </c>
       <c r="S30" t="n">
-        <v>1080752.91</v>
+        <v>1520139.95</v>
       </c>
       <c r="T30" t="n">
-        <v>1150155.83</v>
+        <v>1514122.97</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
       </c>
       <c r="V30" t="n">
-        <v>18278525</v>
+        <v>18269345</v>
       </c>
       <c r="W30" t="n">
         <v>18370086</v>
       </c>
       <c r="X30" t="n">
-        <v>91561</v>
+        <v>100741</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação - PJ</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1522.86</v>
+        <v>4513</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>186346</v>
+        <v>372692</v>
       </c>
       <c r="Q42" t="n">
-        <v>229579.78</v>
+        <v>635623</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5576,13 +5576,13 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>229579.78</v>
+        <v>635623</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>635623</v>
+        <v>1471969</v>
       </c>
       <c r="W42" t="n">
         <v>821969</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>821969</v>
+        <v>1471969</v>
       </c>
       <c r="AA42" t="n">
         <v>5</v>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5690,34 +5690,34 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>1108160.9</v>
+        <v>1399825.3</v>
       </c>
       <c r="R43" t="n">
-        <v>651717.9</v>
+        <v>943158.42</v>
       </c>
       <c r="S43" t="n">
-        <v>651717.9</v>
+        <v>943158.42</v>
       </c>
       <c r="T43" t="n">
-        <v>1108160.9</v>
+        <v>1399825.3</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>16079724</v>
+        <v>15243378</v>
       </c>
       <c r="W43" t="n">
         <v>21072104</v>
       </c>
       <c r="X43" t="n">
-        <v>5144526</v>
+        <v>5330872</v>
       </c>
       <c r="Y43" t="n">
-        <v>34200</v>
+        <v>684200</v>
       </c>
       <c r="Z43" t="n">
-        <v>21037904</v>
+        <v>20387904</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>Sesana - Cresan</t>
+          <t>SESANA - CRESAN</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>CPCA</t>
+          <t>CPCA - Políticas</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9128,22 +9128,22 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>55000</v>
+        <v>56421.78</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>621.9</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>621.9</v>
       </c>
       <c r="T71" t="n">
-        <v>55000</v>
+        <v>55845.78</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10768,14 +10768,14 @@
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
+          <t>Selo Direitos Humanos</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
           <t>Selo DH</t>
         </is>
       </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>Selo DH</t>
-        </is>
-      </c>
       <c r="AE84" t="inlineStr">
         <is>
           <t>Material Permanente</t>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Desaparecidas</t>
+          <t>CLFD</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>Desaparecidas</t>
+          <t>CLFD - Políticas</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Memória e Verdade</t>
+          <t>Direito à Memória e Verdade</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>CPJ</t>
+          <t>CPJ - Políticas</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1201590.23</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>CPD</t>
+          <t>CPD - Políticas</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1054150.07</v>
+        <v>2092306.37</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>ODH</t>
+          <t>ODH - Manutenção</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13433,22 +13433,22 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>216540.94</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>13728.92</v>
+        <v>453625.94</v>
       </c>
       <c r="R106" t="n">
-        <v>13164.1</v>
+        <v>230326.94</v>
       </c>
       <c r="S106" t="n">
-        <v>13164.1</v>
+        <v>230326.94</v>
       </c>
       <c r="T106" t="n">
-        <v>13728.92</v>
+        <v>237085</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPEF</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -13720,12 +13720,12 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>Egressos e Familiares</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>Egressos</t>
+          <t>CPEF - Políticas</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14300,16 +14300,16 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>354272.62</v>
+        <v>390282.46</v>
       </c>
       <c r="R113" t="n">
-        <v>351608.62</v>
+        <v>386131.96</v>
       </c>
       <c r="S113" t="n">
-        <v>351608.62</v>
+        <v>386131.96</v>
       </c>
       <c r="T113" t="n">
-        <v>351608.62</v>
+        <v>387618.46</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>4682693.05</v>
+        <v>4782427.07</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15284,16 +15284,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>1589756.86</v>
+        <v>2277308.83</v>
       </c>
       <c r="R121" t="n">
-        <v>908756.86</v>
+        <v>1189043.86</v>
       </c>
       <c r="S121" t="n">
-        <v>908756.86</v>
+        <v>1189043.86</v>
       </c>
       <c r="T121" t="n">
-        <v>1023556.86</v>
+        <v>1711108.83</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16514,16 +16514,16 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>4938259.32</v>
+        <v>4938711.33</v>
       </c>
       <c r="R131" t="n">
-        <v>469142.51</v>
+        <v>469482.58</v>
       </c>
       <c r="S131" t="n">
-        <v>469142.51</v>
+        <v>469482.58</v>
       </c>
       <c r="T131" t="n">
-        <v>4938259.32</v>
+        <v>4938711.33</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="AD135" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AE135" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17735,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>35663951.76</v>
+        <v>36560879.15</v>
       </c>
       <c r="O141" t="n">
         <v>19269551.01</v>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -17907,7 +17907,7 @@
       </c>
       <c r="AD142" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE142" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18030,7 +18030,7 @@
       </c>
       <c r="AD143" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE143" t="inlineStr">
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="AD144" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE144" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2592000</v>
+        <v>2628000</v>
       </c>
       <c r="O145" t="n">
         <v>180000</v>
@@ -18276,7 +18276,7 @@
       </c>
       <c r="AD145" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE145" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="AD146" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE146" t="inlineStr">
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="AD147" t="inlineStr">
         <is>
-          <t>Sesana - Políticas</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE147" t="inlineStr">
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -18891,12 +18891,12 @@
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>Serv. de Tec. da Inf. e Com - PJ</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>9072713.01</v>
+        <v>10476334.32</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19088,7 +19088,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>4701260.65</v>
+        <v>6695961.38</v>
       </c>
       <c r="O152" t="n">
         <v>3068431.98</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>13/02/2026 07:41:46</t>
+          <t>18/02/2026 17:50:18</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>535673.5699999999</v>
+        <v>1443170.97</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1142,10 +1142,10 @@
         <v>7231</v>
       </c>
       <c r="R6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="S6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="T6" t="n">
         <v>7231</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>11571411.55</v>
+        <v>11781995.49</v>
       </c>
       <c r="R10" t="n">
-        <v>4825017.69</v>
+        <v>7301759.09</v>
       </c>
       <c r="S10" t="n">
-        <v>4827038.33</v>
+        <v>7303779.73</v>
       </c>
       <c r="T10" t="n">
-        <v>11028396.09</v>
+        <v>11238980.03</v>
       </c>
       <c r="U10" t="n">
         <v>2020.64</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3599,16 +3599,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>26530.2</v>
+        <v>277242.74</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>250712.54</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>250712.54</v>
       </c>
       <c r="T26" t="n">
-        <v>26530.2</v>
+        <v>277242.74</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1516933.95</v>
+        <v>9476248.34</v>
       </c>
       <c r="R30" t="n">
-        <v>1513567.3</v>
+        <v>4308561.59</v>
       </c>
       <c r="S30" t="n">
-        <v>1520139.95</v>
+        <v>4315134.24</v>
       </c>
       <c r="T30" t="n">
-        <v>1514122.97</v>
+        <v>9473437.359999999</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5561,13 +5561,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>406043.22</v>
       </c>
       <c r="P42" t="n">
         <v>372692</v>
       </c>
       <c r="Q42" t="n">
-        <v>635623</v>
+        <v>1866731.38</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>635623</v>
+        <v>1460688.16</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5690,16 +5690,16 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>1399825.3</v>
+        <v>1533015.46</v>
       </c>
       <c r="R43" t="n">
-        <v>943158.42</v>
+        <v>1030855.66</v>
       </c>
       <c r="S43" t="n">
-        <v>943158.42</v>
+        <v>1030855.66</v>
       </c>
       <c r="T43" t="n">
-        <v>1399825.3</v>
+        <v>1533015.46</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>122450</v>
+        <v>244900</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9134,16 +9134,16 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>56421.78</v>
+        <v>254990.22</v>
       </c>
       <c r="R71" t="n">
-        <v>621.9</v>
+        <v>131366.56</v>
       </c>
       <c r="S71" t="n">
-        <v>621.9</v>
+        <v>131366.56</v>
       </c>
       <c r="T71" t="n">
-        <v>55845.78</v>
+        <v>254414.22</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>779600</v>
+        <v>1576800</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1794</v>
+        <v>3394</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>2664000</v>
+        <v>3744000</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 07:02:44</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>535673.5699999999</v>
+        <v>1443170.97</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1142,10 +1142,10 @@
         <v>7231</v>
       </c>
       <c r="R6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="S6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="T6" t="n">
         <v>7231</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>11571411.55</v>
+        <v>11781995.49</v>
       </c>
       <c r="R10" t="n">
-        <v>4825017.69</v>
+        <v>7301759.09</v>
       </c>
       <c r="S10" t="n">
-        <v>4827038.33</v>
+        <v>7303779.73</v>
       </c>
       <c r="T10" t="n">
-        <v>11028396.09</v>
+        <v>11238980.03</v>
       </c>
       <c r="U10" t="n">
         <v>2020.64</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3599,16 +3599,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>26530.2</v>
+        <v>277242.74</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>250712.54</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>250712.54</v>
       </c>
       <c r="T26" t="n">
-        <v>26530.2</v>
+        <v>277242.74</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1516933.95</v>
+        <v>9476248.34</v>
       </c>
       <c r="R30" t="n">
-        <v>1513567.3</v>
+        <v>4308561.59</v>
       </c>
       <c r="S30" t="n">
-        <v>1520139.95</v>
+        <v>4315134.24</v>
       </c>
       <c r="T30" t="n">
-        <v>1514122.97</v>
+        <v>9473437.359999999</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>Planejamento e Informação</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5561,13 +5561,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>406043.22</v>
       </c>
       <c r="P42" t="n">
         <v>372692</v>
       </c>
       <c r="Q42" t="n">
-        <v>635623</v>
+        <v>1866731.38</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>635623</v>
+        <v>1460688.16</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5690,16 +5690,16 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>1399825.3</v>
+        <v>1533015.46</v>
       </c>
       <c r="R43" t="n">
-        <v>943158.42</v>
+        <v>1030855.66</v>
       </c>
       <c r="S43" t="n">
-        <v>943158.42</v>
+        <v>1030855.66</v>
       </c>
       <c r="T43" t="n">
-        <v>1399825.3</v>
+        <v>1533015.46</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>122450</v>
+        <v>244900</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9134,16 +9134,16 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>56421.78</v>
+        <v>254990.22</v>
       </c>
       <c r="R71" t="n">
-        <v>621.9</v>
+        <v>131366.56</v>
       </c>
       <c r="S71" t="n">
-        <v>621.9</v>
+        <v>131366.56</v>
       </c>
       <c r="T71" t="n">
-        <v>55845.78</v>
+        <v>254414.22</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13848,7 +13848,7 @@
       </c>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -13971,7 +13971,7 @@
       </c>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="AD111" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE111" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="AD113" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE113" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="AD114" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE114" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AD115" t="inlineStr">
         <is>
-          <t>CPM - CMB</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE115" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>779600</v>
+        <v>1576800</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>1794</v>
+        <v>3394</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>2664000</v>
+        <v>3744000</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>18/02/2026 17:50:18</t>
+          <t>19/02/2026 15:00:22</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>8263.299999999999</v>
+        <v>113263.3</v>
       </c>
       <c r="R7" t="n">
         <v>5651</v>
@@ -1271,7 +1271,7 @@
         <v>5651</v>
       </c>
       <c r="T7" t="n">
-        <v>8263.299999999999</v>
+        <v>113263.3</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>107.79</v>
       </c>
       <c r="O11" t="n">
         <v>200450</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>767852.36</v>
+        <v>806249</v>
       </c>
       <c r="R19" t="n">
         <v>405385.74</v>
@@ -2747,7 +2747,7 @@
         <v>405385.74</v>
       </c>
       <c r="T19" t="n">
-        <v>767852.36</v>
+        <v>806249</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -3848,10 +3848,10 @@
         <v>2034431.44</v>
       </c>
       <c r="R28" t="n">
-        <v>1393557.25</v>
+        <v>1485288.62</v>
       </c>
       <c r="S28" t="n">
-        <v>1505940.38</v>
+        <v>1597671.75</v>
       </c>
       <c r="T28" t="n">
         <v>1832556</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4094,10 +4094,10 @@
         <v>9476248.34</v>
       </c>
       <c r="R30" t="n">
-        <v>4308561.59</v>
+        <v>6511713.92</v>
       </c>
       <c r="S30" t="n">
-        <v>4315134.24</v>
+        <v>6518286.57</v>
       </c>
       <c r="T30" t="n">
         <v>9473437.359999999</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2034382.45</v>
       </c>
       <c r="O47" t="n">
         <v>4140329.7</v>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>333946.2</v>
+        <v>2231063.83</v>
       </c>
       <c r="O117" t="n">
         <v>1425517.51</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>40640152.52</v>
+        <v>40666752.17</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>36560879.15</v>
+        <v>39714269.98</v>
       </c>
       <c r="O141" t="n">
         <v>19269551.01</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18251,7 +18251,7 @@
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>80849746</v>
+        <v>79443026</v>
       </c>
       <c r="W145" t="n">
         <v>83642123</v>
@@ -18260,10 +18260,10 @@
         <v>2792377</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="Z145" t="n">
-        <v>83642123</v>
+        <v>82235403</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18470,7 +18470,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -18497,7 +18497,7 @@
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="W147" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>
@@ -19088,7 +19088,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>6695961.38</v>
+        <v>6837203.26</v>
       </c>
       <c r="O152" t="n">
         <v>3068431.98</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>19/02/2026 15:00:22</t>
+          <t>20/02/2026 10:39:51</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>194146.21</v>
+        <v>197546.21</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>806249</v>
+        <v>864959</v>
       </c>
       <c r="R19" t="n">
         <v>405385.74</v>
@@ -2747,7 +2747,7 @@
         <v>405385.74</v>
       </c>
       <c r="T19" t="n">
-        <v>806249</v>
+        <v>864959</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>33707.98</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4565,16 +4565,16 @@
         </is>
       </c>
       <c r="K34" t="n">
+        <v>275631.58</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>5192.79</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4513</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>390282.46</v>
+        <v>1404203.24</v>
       </c>
       <c r="R113" t="n">
         <v>386131.96</v>
@@ -14309,7 +14309,7 @@
         <v>386131.96</v>
       </c>
       <c r="T113" t="n">
-        <v>387618.46</v>
+        <v>1401539.24</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>40666752.17</v>
+        <v>40816540.35</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17738,7 +17738,7 @@
         <v>39714269.98</v>
       </c>
       <c r="O141" t="n">
-        <v>19269551.01</v>
+        <v>19488782.86</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -17747,16 +17747,16 @@
         <v>147777170.7</v>
       </c>
       <c r="R141" t="n">
-        <v>109372086.03</v>
+        <v>114195186.71</v>
       </c>
       <c r="S141" t="n">
-        <v>112181016.23</v>
+        <v>119634899.1</v>
       </c>
       <c r="T141" t="n">
-        <v>128507619.69</v>
+        <v>128288387.84</v>
       </c>
       <c r="U141" t="n">
-        <v>2808930.2</v>
+        <v>5439712.39</v>
       </c>
       <c r="V141" t="n">
         <v>166077092</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18482,7 +18482,7 @@
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
@@ -18491,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>10476334.32</v>
+        <v>10767141.25</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>20/02/2026 10:39:51</t>
+          <t>21/02/2026 06:41:50</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>21/02/2026 06:41:50</t>
+          <t>22/02/2026 06:46:03</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>22/02/2026 06:46:03</t>
+          <t>23/02/2026 07:09:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>264605.68</v>
+        <v>505273.57</v>
       </c>
       <c r="O3" t="n">
         <v>21963.73</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>12545</v>
+        <v>190046.21</v>
       </c>
       <c r="O10" t="n">
         <v>543015.46</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>124658.62</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>157713.7</v>
+        <v>157814.59</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>110.08</v>
+        <v>149384.58</v>
       </c>
       <c r="O28" t="n">
         <v>201875.44</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4073,16 +4073,16 @@
         </is>
       </c>
       <c r="K30" t="n">
+        <v>47624.92</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>40624.92</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>2810.98</v>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9476248.34</v>
+        <v>9680314.58</v>
       </c>
       <c r="R30" t="n">
-        <v>6511713.92</v>
+        <v>9062818.300000001</v>
       </c>
       <c r="S30" t="n">
-        <v>6518286.57</v>
+        <v>9069390.949999999</v>
       </c>
       <c r="T30" t="n">
-        <v>9473437.359999999</v>
+        <v>9677503.6</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5192.79</v>
+        <v>275631.58</v>
       </c>
       <c r="O34" t="n">
         <v>2931914.44</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>5663.52</v>
+        <v>31441.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5690,7 +5690,7 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>1533015.46</v>
+        <v>2243254.85</v>
       </c>
       <c r="R43" t="n">
         <v>1030855.66</v>
@@ -5699,7 +5699,7 @@
         <v>1030855.66</v>
       </c>
       <c r="T43" t="n">
-        <v>1533015.46</v>
+        <v>2243254.85</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11831,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1201590.23</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14054,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>11808</v>
+        <v>98641.25</v>
       </c>
       <c r="R111" t="n">
         <v>11808</v>
@@ -14063,7 +14063,7 @@
         <v>11808</v>
       </c>
       <c r="T111" t="n">
-        <v>11808</v>
+        <v>98641.25</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14294,25 +14294,25 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>2664</v>
+        <v>607317.37</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>1404203.24</v>
+        <v>5048475.3</v>
       </c>
       <c r="R113" t="n">
-        <v>386131.96</v>
+        <v>540078.12</v>
       </c>
       <c r="S113" t="n">
-        <v>386131.96</v>
+        <v>540398.12</v>
       </c>
       <c r="T113" t="n">
-        <v>1401539.24</v>
+        <v>4441157.93</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="V113" t="n">
         <v>4701261</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2231063.83</v>
+        <v>4782427.07</v>
       </c>
       <c r="O117" t="n">
         <v>1425517.51</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>3394</v>
+        <v>43983</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>11112.8</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17735,25 +17735,25 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>39714269.98</v>
+        <v>40640152.52</v>
       </c>
       <c r="O141" t="n">
-        <v>19488782.86</v>
+        <v>19947440.86</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>147777170.7</v>
+        <v>150428147.19</v>
       </c>
       <c r="R141" t="n">
-        <v>114195186.71</v>
+        <v>115924287.71</v>
       </c>
       <c r="S141" t="n">
-        <v>119634899.1</v>
+        <v>121364000.1</v>
       </c>
       <c r="T141" t="n">
-        <v>128288387.84</v>
+        <v>130480706.33</v>
       </c>
       <c r="U141" t="n">
         <v>5439712.39</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18104,25 +18104,25 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2949590.4</v>
+        <v>5410565.4</v>
       </c>
       <c r="O144" t="n">
-        <v>26317219.2</v>
+        <v>29453556.8</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>52634438.4</v>
+        <v>58907113.6</v>
       </c>
       <c r="R144" t="n">
-        <v>26317219.2</v>
+        <v>29453556.8</v>
       </c>
       <c r="S144" t="n">
-        <v>26317219.2</v>
+        <v>29453556.8</v>
       </c>
       <c r="T144" t="n">
-        <v>26317219.2</v>
+        <v>29453556.8</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2628000</v>
+        <v>2664000</v>
       </c>
       <c r="O145" t="n">
         <v>180000</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18485,10 +18485,10 @@
         <v>1406720</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T147" t="n">
         <v>1406720</v>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>10767141.25</v>
+        <v>12347308.94</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19088,7 +19088,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>6837203.26</v>
+        <v>8742838.41</v>
       </c>
       <c r="O152" t="n">
         <v>3068431.98</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>23/02/2026 07:09:23</t>
+          <t>24/02/2026 07:09:02</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>505273.57</v>
+        <v>535673.5699999999</v>
       </c>
       <c r="O3" t="n">
         <v>21963.73</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>197546.21</v>
+        <v>251299.99</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>40389.32</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2732,22 +2732,22 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2750000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>864959</v>
+        <v>8440644</v>
       </c>
       <c r="R19" t="n">
-        <v>405385.74</v>
+        <v>4773431.1</v>
       </c>
       <c r="S19" t="n">
-        <v>405385.74</v>
+        <v>4773431.1</v>
       </c>
       <c r="T19" t="n">
-        <v>864959</v>
+        <v>5690644</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1326292.86</v>
+        <v>2677638.29</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3353,16 +3353,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1326292.86</v>
+        <v>2677638.29</v>
       </c>
       <c r="R24" t="n">
-        <v>1326292.86</v>
+        <v>2677638.29</v>
       </c>
       <c r="S24" t="n">
-        <v>1326292.86</v>
+        <v>2677638.29</v>
       </c>
       <c r="T24" t="n">
-        <v>1326292.86</v>
+        <v>2677638.29</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>149384.58</v>
+        <v>157713.7</v>
       </c>
       <c r="O28" t="n">
         <v>201875.44</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>47624.92</v>
+        <v>163460.74</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>33707.98</v>
+        <v>38322.58</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>379194.76</v>
+        <v>729553.4399999999</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4460,16 +4460,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>379194.76</v>
+        <v>729553.4399999999</v>
       </c>
       <c r="R33" t="n">
-        <v>379194.76</v>
+        <v>729553.4399999999</v>
       </c>
       <c r="S33" t="n">
-        <v>379194.76</v>
+        <v>729553.4399999999</v>
       </c>
       <c r="T33" t="n">
-        <v>379194.76</v>
+        <v>729553.4399999999</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5570,10 +5570,10 @@
         <v>1866731.38</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>229579.78</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>229579.78</v>
       </c>
       <c r="T42" t="n">
         <v>1460688.16</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5693,10 +5693,10 @@
         <v>2243254.85</v>
       </c>
       <c r="R43" t="n">
-        <v>1030855.66</v>
+        <v>1636952.03</v>
       </c>
       <c r="S43" t="n">
-        <v>1030855.66</v>
+        <v>1636952.03</v>
       </c>
       <c r="T43" t="n">
         <v>2243254.85</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2459898.9</v>
+        <v>2861229.41</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13802,16 +13802,16 @@
         <v>1221823</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>4887292</v>
+        <v>5281025.59</v>
       </c>
       <c r="R109" t="n">
-        <v>4887292</v>
+        <v>4493558.41</v>
       </c>
       <c r="S109" t="n">
         <v>4887292</v>
@@ -13820,7 +13820,7 @@
         <v>4887292</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
+        <v>393733.59</v>
       </c>
       <c r="V109" t="n">
         <v>4887292</v>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14057,10 +14057,10 @@
         <v>98641.25</v>
       </c>
       <c r="R111" t="n">
-        <v>11808</v>
+        <v>33311.56</v>
       </c>
       <c r="S111" t="n">
-        <v>11808</v>
+        <v>33311.56</v>
       </c>
       <c r="T111" t="n">
         <v>98641.25</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>607317.37</v>
+        <v>1621238.15</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
@@ -14303,13 +14303,13 @@
         <v>5048475.3</v>
       </c>
       <c r="R113" t="n">
-        <v>540078.12</v>
+        <v>1291768.13</v>
       </c>
       <c r="S113" t="n">
-        <v>540398.12</v>
+        <v>1292088.13</v>
       </c>
       <c r="T113" t="n">
-        <v>4441157.93</v>
+        <v>3427237.15</v>
       </c>
       <c r="U113" t="n">
         <v>320</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>4782427.07</v>
+        <v>5027120.48</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15164,10 +15164,10 @@
         <v>364021.94</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="S120" t="n">
-        <v>57214.44</v>
+        <v>114428.88</v>
       </c>
       <c r="T120" t="n">
         <v>364021.94</v>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15266,7 +15266,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>24906.96</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -15284,16 +15284,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2277308.83</v>
+        <v>2647748.79</v>
       </c>
       <c r="R121" t="n">
-        <v>1189043.86</v>
+        <v>1532043.86</v>
       </c>
       <c r="S121" t="n">
-        <v>1189043.86</v>
+        <v>1532043.86</v>
       </c>
       <c r="T121" t="n">
-        <v>1711108.83</v>
+        <v>2081548.79</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17744,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>150428147.19</v>
+        <v>154812784.17</v>
       </c>
       <c r="R141" t="n">
         <v>115924287.71</v>
@@ -17753,7 +17753,7 @@
         <v>121364000.1</v>
       </c>
       <c r="T141" t="n">
-        <v>130480706.33</v>
+        <v>134865343.31</v>
       </c>
       <c r="U141" t="n">
         <v>5439712.39</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>3744000</v>
+        <v>4042120.9</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>12347308.94</v>
+        <v>13758108.3</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19088,7 +19088,7 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>8742838.41</v>
+        <v>9072713.01</v>
       </c>
       <c r="O152" t="n">
         <v>3068431.98</v>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>24/02/2026 07:09:02</t>
+          <t>25/02/2026 07:09:50</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG152"/>
+  <dimension ref="A1:AG153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1443170.97</v>
+        <v>1844144.91</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>34200</v>
+        <v>128086</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>84200</v>
+        <v>178086</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -902,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>84200</v>
+        <v>178086</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>84200</v>
+        <v>178086</v>
       </c>
       <c r="W4" t="n">
         <v>50000</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>84200</v>
+        <v>178086</v>
       </c>
       <c r="AA4" t="n">
         <v>5</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4984</v>
+        <v>7231</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>11257.26</v>
       </c>
       <c r="O8" t="n">
-        <v>140000</v>
+        <v>161083.4</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>260000</v>
+        <v>403170.4</v>
       </c>
       <c r="R8" t="n">
-        <v>120000</v>
+        <v>191768.25</v>
       </c>
       <c r="S8" t="n">
-        <v>120000</v>
+        <v>191768.25</v>
       </c>
       <c r="T8" t="n">
-        <v>120000</v>
+        <v>242087</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1625,25 +1625,25 @@
         <v>190046.21</v>
       </c>
       <c r="O10" t="n">
-        <v>543015.46</v>
+        <v>566386.21</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>11781995.49</v>
+        <v>11905366.24</v>
       </c>
       <c r="R10" t="n">
-        <v>7301759.09</v>
+        <v>7401759.09</v>
       </c>
       <c r="S10" t="n">
-        <v>7303779.73</v>
+        <v>7415547.98</v>
       </c>
       <c r="T10" t="n">
-        <v>11238980.03</v>
+        <v>11338980.03</v>
       </c>
       <c r="U10" t="n">
-        <v>2020.64</v>
+        <v>13788.89</v>
       </c>
       <c r="V10" t="n">
         <v>12568415</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>9709.27</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>9709.27</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2255,13 +2255,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>9709.27</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9709.27</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>9709.27</v>
       </c>
       <c r="AA15" t="n">
         <v>5</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         <v>9180</v>
       </c>
       <c r="Q28" t="n">
-        <v>2034431.44</v>
+        <v>2034582.74</v>
       </c>
       <c r="R28" t="n">
         <v>1485288.62</v>
@@ -3854,7 +3854,7 @@
         <v>1597671.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1832556</v>
+        <v>1832707.3</v>
       </c>
       <c r="U28" t="n">
         <v>112383.13</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>163460.74</v>
+        <v>376030.34</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4091,16 +4091,16 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>9680314.58</v>
+        <v>17186912.55</v>
       </c>
       <c r="R30" t="n">
-        <v>9062818.300000001</v>
+        <v>16569256.04</v>
       </c>
       <c r="S30" t="n">
-        <v>9069390.949999999</v>
+        <v>16575828.69</v>
       </c>
       <c r="T30" t="n">
-        <v>9677503.6</v>
+        <v>17184101.57</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5690,22 +5690,22 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>2243254.85</v>
+        <v>3739123.62</v>
       </c>
       <c r="R43" t="n">
-        <v>1636952.03</v>
+        <v>3126496.8</v>
       </c>
       <c r="S43" t="n">
-        <v>1636952.03</v>
+        <v>3126496.8</v>
       </c>
       <c r="T43" t="n">
-        <v>2243254.85</v>
+        <v>3739123.62</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>15243378</v>
+        <v>15139782.73</v>
       </c>
       <c r="W43" t="n">
         <v>21072104</v>
@@ -5714,10 +5714,10 @@
         <v>5330872</v>
       </c>
       <c r="Y43" t="n">
-        <v>684200</v>
+        <v>787795.27</v>
       </c>
       <c r="Z43" t="n">
-        <v>20387904</v>
+        <v>20284308.73</v>
       </c>
       <c r="AA43" t="n">
         <v>5</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>3430</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10118,16 +10118,16 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>73843.36</v>
+        <v>416595.36</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>327600</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>327600</v>
       </c>
       <c r="T79" t="n">
-        <v>50000</v>
+        <v>392752</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -12947,16 +12947,16 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>6953424.46</v>
+        <v>7686397.08</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>732972.62</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>732972.62</v>
       </c>
       <c r="T102" t="n">
-        <v>6953424.46</v>
+        <v>7686397.08</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14519,12 +14519,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>44905200</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -14564,16 +14564,16 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
         <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>5</v>
@@ -14591,17 +14591,17 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>Aquisição de Material Permanente</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Código Genérico</t>
         </is>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
         <v>4025</v>
       </c>
       <c r="G116" t="n">
-        <v>4329</v>
+        <v>2053</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>33904800</t>
+          <t>44905200</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -14660,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14669,34 +14669,34 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1576800</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>2356400</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>779600</v>
+        <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>8578400</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="X116" t="n">
-        <v>1421600</v>
+        <v>10000</v>
       </c>
       <c r="Y116" t="n">
         <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>10000000</v>
+        <v>10000</v>
       </c>
       <c r="AA116" t="n">
         <v>5</v>
@@ -14709,12 +14709,12 @@
       </c>
       <c r="AD116" t="inlineStr">
         <is>
-          <t>CPM - Políticas</t>
+          <t>CPM - Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
+          <t>Aquisição de Material Permanente</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14756,7 @@
         <v>4025</v>
       </c>
       <c r="G117" t="n">
-        <v>6178</v>
+        <v>4329</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904800</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>5027120.48</v>
+        <v>1576800</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14783,43 +14783,43 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4782427.07</v>
+        <v>1576800</v>
       </c>
       <c r="O117" t="n">
-        <v>1425517.51</v>
+        <v>0</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>23851875.51</v>
+        <v>8578400</v>
       </c>
       <c r="R117" t="n">
-        <v>21926109.23</v>
+        <v>1576800</v>
       </c>
       <c r="S117" t="n">
-        <v>22593123.43</v>
+        <v>2356400</v>
       </c>
       <c r="T117" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="U117" t="n">
-        <v>667014.2</v>
+        <v>779600</v>
       </c>
       <c r="V117" t="n">
-        <v>22426358</v>
+        <v>8578400</v>
       </c>
       <c r="W117" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>1421600</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>22426358</v>
+        <v>10000000</v>
       </c>
       <c r="AA117" t="n">
         <v>5</v>
@@ -14832,12 +14832,12 @@
       </c>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>CPM - Equipamentos</t>
+          <t>CPM - Políticas</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Outros Auxílios Financeiros - Pessoas Físicas</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>43983</v>
+        <v>5027120.48</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14906,34 +14906,34 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4782427.07</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>1425517.51</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>108749.82</v>
+        <v>23851875.51</v>
       </c>
       <c r="R118" t="n">
-        <v>64653</v>
+        <v>21926109.23</v>
       </c>
       <c r="S118" t="n">
-        <v>66447</v>
+        <v>22593123.43</v>
       </c>
       <c r="T118" t="n">
-        <v>108749.82</v>
+        <v>22426358</v>
       </c>
       <c r="U118" t="n">
-        <v>1794</v>
+        <v>667014.2</v>
       </c>
       <c r="V118" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="W118" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14942,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>200000</v>
+        <v>22426358</v>
       </c>
       <c r="AA118" t="n">
         <v>5</v>
@@ -14960,7 +14960,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15020,7 +15020,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>11112.8</v>
+        <v>43983</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -15029,7 +15029,7 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>11112.8</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15038,25 +15038,25 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>88531.96000000001</v>
+        <v>108749.82</v>
       </c>
       <c r="R119" t="n">
-        <v>88531.96000000001</v>
+        <v>64653</v>
       </c>
       <c r="S119" t="n">
-        <v>88531.96000000001</v>
+        <v>66447</v>
       </c>
       <c r="T119" t="n">
-        <v>88531.96000000001</v>
+        <v>108749.82</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="V119" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="W119" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -15065,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="AA119" t="n">
         <v>5</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>11112.8</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -15152,7 +15152,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>11112.8</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15161,25 +15161,25 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>364021.94</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="R120" t="n">
-        <v>57214.44</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="S120" t="n">
-        <v>114428.88</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="T120" t="n">
-        <v>364021.94</v>
+        <v>88531.96000000001</v>
       </c>
       <c r="U120" t="n">
-        <v>57214.44</v>
+        <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="W120" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>2537927</v>
+        <v>250000</v>
       </c>
       <c r="AA120" t="n">
         <v>5</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -15266,7 +15266,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>24906.96</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -15278,31 +15278,31 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>566200</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2647748.79</v>
+        <v>364021.94</v>
       </c>
       <c r="R121" t="n">
-        <v>1532043.86</v>
+        <v>57214.44</v>
       </c>
       <c r="S121" t="n">
-        <v>1532043.86</v>
+        <v>114428.88</v>
       </c>
       <c r="T121" t="n">
-        <v>2081548.79</v>
+        <v>364021.94</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>57214.44</v>
       </c>
       <c r="V121" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="W121" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="X121" t="n">
         <v>0</v>
@@ -15311,7 +15311,7 @@
         <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>4806049</v>
+        <v>2537927</v>
       </c>
       <c r="AA121" t="n">
         <v>5</v>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15385,11 +15385,11 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>24906.96</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -15401,31 +15401,31 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>566200</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>80000</v>
+        <v>2854466.54</v>
       </c>
       <c r="R122" t="n">
-        <v>80000</v>
+        <v>1738210.53</v>
       </c>
       <c r="S122" t="n">
-        <v>80000</v>
+        <v>1738210.53</v>
       </c>
       <c r="T122" t="n">
-        <v>80000</v>
+        <v>2288266.54</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="W122" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="X122" t="n">
         <v>0</v>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>139282</v>
+        <v>4806049</v>
       </c>
       <c r="AA122" t="n">
         <v>5</v>
@@ -15457,12 +15457,12 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15503,16 +15503,16 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>33904700</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>1967.85</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1967.85</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15530,25 +15530,25 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="R123" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="S123" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="T123" t="n">
-        <v>19678.5</v>
+        <v>80000</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="W123" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="X123" t="n">
         <v>0</v>
@@ -15557,7 +15557,7 @@
         <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>49000</v>
+        <v>139282</v>
       </c>
       <c r="AA123" t="n">
         <v>5</v>
@@ -15575,17 +15575,17 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>Obrigações Tributárias e Contributivas</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15617,16 +15617,16 @@
         <v>4025</v>
       </c>
       <c r="G124" t="n">
-        <v>9027</v>
+        <v>6178</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33904700</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -15635,7 +15635,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -15644,7 +15644,7 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1967.85</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15653,34 +15653,34 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>19678.5</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="W124" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="X124" t="n">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
         <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>110000</v>
+        <v>49000</v>
       </c>
       <c r="AA124" t="n">
         <v>5</v>
@@ -15688,17 +15688,17 @@
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPM - Equipamentos</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obrigações Tributárias e Contributivas</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15740,7 +15740,7 @@
         <v>4025</v>
       </c>
       <c r="G125" t="n">
-        <v>9030</v>
+        <v>9027</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -15794,16 +15794,16 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="X125" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="AA125" t="n">
         <v>5</v>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15863,7 @@
         <v>4025</v>
       </c>
       <c r="G126" t="n">
-        <v>9044</v>
+        <v>9030</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -15917,16 +15917,16 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="X126" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="AA126" t="n">
         <v>5</v>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -15983,19 +15983,19 @@
         <v>422</v>
       </c>
       <c r="F127" t="n">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="G127" t="n">
-        <v>4327</v>
+        <v>9044</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>CPIR</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -16037,19 +16037,19 @@
         <v>0</v>
       </c>
       <c r="V127" t="n">
-        <v>11949</v>
+        <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Y127" t="n">
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>11949</v>
+        <v>75000</v>
       </c>
       <c r="AA127" t="n">
         <v>5</v>
@@ -16057,17 +16057,17 @@
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Igualdade Racial</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
         <is>
-          <t>CPIR - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
         <v>4026</v>
       </c>
       <c r="G128" t="n">
-        <v>4334</v>
+        <v>4327</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -16142,37 +16142,37 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>3595409.87</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>3596273</v>
+        <v>11949</v>
       </c>
       <c r="W128" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="X128" t="n">
-        <v>2986219</v>
+        <v>0</v>
       </c>
       <c r="Y128" t="n">
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>6455492</v>
+        <v>11949</v>
       </c>
       <c r="AA128" t="n">
         <v>5</v>
@@ -16185,12 +16185,12 @@
       </c>
       <c r="AD128" t="inlineStr">
         <is>
-          <t>CPIR - Equipamentos</t>
+          <t>CPIR - Políticas</t>
         </is>
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>33903100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -16265,37 +16265,37 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>3595409.87</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>5374</v>
+        <v>3596273</v>
       </c>
       <c r="W129" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="X129" t="n">
-        <v>4626</v>
+        <v>2986219</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>10000</v>
+        <v>6455492</v>
       </c>
       <c r="AA129" t="n">
         <v>5</v>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>Premiações Culturais, Artísticas e outras</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>33903700</t>
+          <t>33903100</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -16406,19 +16406,19 @@
         <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>80612</v>
+        <v>5374</v>
       </c>
       <c r="W130" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="X130" t="n">
-        <v>69388</v>
+        <v>4626</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="AA130" t="n">
         <v>5</v>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>Locação de Mão de Obra</t>
+          <t>Premiações Culturais, Artísticas e outras</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903700</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -16514,34 +16514,34 @@
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>4938711.33</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>469482.58</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>469482.58</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>4938711.33</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>5870981</v>
+        <v>80612</v>
       </c>
       <c r="W131" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="X131" t="n">
-        <v>5054381</v>
+        <v>69388</v>
       </c>
       <c r="Y131" t="n">
         <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>10925362</v>
+        <v>150000</v>
       </c>
       <c r="AA131" t="n">
         <v>5</v>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Locação de Mão de Obra</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16615,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -16631,40 +16631,40 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>225</v>
+        <v>551.08</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>525</v>
+        <v>5013837.31</v>
       </c>
       <c r="R132" t="n">
-        <v>300</v>
+        <v>543230.86</v>
       </c>
       <c r="S132" t="n">
-        <v>300</v>
+        <v>543230.86</v>
       </c>
       <c r="T132" t="n">
-        <v>300</v>
+        <v>5013286.23</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>1000</v>
+        <v>5870981</v>
       </c>
       <c r="W132" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="X132" t="n">
-        <v>0</v>
+        <v>5054381</v>
       </c>
       <c r="Y132" t="n">
         <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1000</v>
+        <v>10925362</v>
       </c>
       <c r="AA132" t="n">
         <v>5</v>
@@ -16687,12 +16687,12 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>Recursos destinados ao pagamento de concessionárias</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16724,21 +16724,21 @@
         <v>4026</v>
       </c>
       <c r="G133" t="n">
-        <v>9025</v>
+        <v>4334</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -16754,40 +16754,40 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S133" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T133" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W133" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="X133" t="n">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="Y133" t="n">
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>75000</v>
+        <v>1000</v>
       </c>
       <c r="AA133" t="n">
         <v>5</v>
@@ -16795,27 +16795,27 @@
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Igualdade Racial</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>CPIR - Equipamentos</t>
         </is>
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Recursos destinados ao pagamento de concessionárias</t>
         </is>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16841,22 +16841,22 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F134" t="n">
         <v>4026</v>
       </c>
       <c r="G134" t="n">
-        <v>4322</v>
+        <v>9025</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>COPIND</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>33903600</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -16898,19 +16898,19 @@
         <v>0</v>
       </c>
       <c r="V134" t="n">
-        <v>7143</v>
+        <v>0</v>
       </c>
       <c r="W134" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="X134" t="n">
-        <v>39738</v>
+        <v>75000</v>
       </c>
       <c r="Y134" t="n">
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>46881</v>
+        <v>75000</v>
       </c>
       <c r="AA134" t="n">
         <v>5</v>
@@ -16918,17 +16918,17 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Povos Originários</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
         <is>
-          <t>COPIND - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>Contratação PF</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903600</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -17006,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -17015,25 +17015,25 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>33669</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>33669</v>
+        <v>7143</v>
       </c>
       <c r="W135" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="X135" t="n">
-        <v>187297</v>
+        <v>39738</v>
       </c>
       <c r="Y135" t="n">
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>220966</v>
+        <v>46881</v>
       </c>
       <c r="AA135" t="n">
         <v>5</v>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PF</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17093,16 +17093,16 @@
         <v>4026</v>
       </c>
       <c r="G136" t="n">
-        <v>9234</v>
+        <v>4322</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -17129,7 +17129,7 @@
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="R136" t="n">
         <v>0</v>
@@ -17138,25 +17138,25 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>33669</v>
       </c>
       <c r="W136" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="X136" t="n">
-        <v>100000</v>
+        <v>187297</v>
       </c>
       <c r="Y136" t="n">
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>100000</v>
+        <v>220966</v>
       </c>
       <c r="AA136" t="n">
         <v>5</v>
@@ -17164,17 +17164,17 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>Povos Originários</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>COPIND - Políticas</t>
         </is>
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17196,12 +17196,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>FUMCAF</t>
+          <t>SMDHC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -17210,22 +17210,22 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F137" t="n">
-        <v>4010</v>
+        <v>4026</v>
       </c>
       <c r="G137" t="n">
-        <v>4426</v>
+        <v>9234</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -17270,16 +17270,16 @@
         <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="X137" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>589773</v>
+        <v>100000</v>
       </c>
       <c r="AA137" t="n">
         <v>5</v>
@@ -17287,17 +17287,17 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Segurança Alimentar</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Emenda</t>
         </is>
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -17307,48 +17307,48 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>FUMCAF</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>244</v>
+        <v>422</v>
       </c>
       <c r="F138" t="n">
         <v>4010</v>
       </c>
       <c r="G138" t="n">
-        <v>4302</v>
+        <v>4426</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>6470104.18</v>
+        <v>0</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -17366,7 +17366,7 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>6470104.18</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17375,34 +17375,34 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>38820625.08</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>40835555</v>
+        <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="X138" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="Y138" t="n">
         <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>40835555</v>
+        <v>589773</v>
       </c>
       <c r="AA138" t="n">
         <v>5</v>
@@ -17415,12 +17415,12 @@
       </c>
       <c r="AD138" t="inlineStr">
         <is>
-          <t>FAASP</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>44905100</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -17480,7 +17480,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>6470104.18</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -17489,7 +17489,7 @@
         <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>6470104.18</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17498,34 +17498,34 @@
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>38820625.08</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>600437</v>
+        <v>40835555</v>
       </c>
       <c r="W139" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="X139" t="n">
-        <v>16295665</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
         <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>16896102</v>
+        <v>40835555</v>
       </c>
       <c r="AA139" t="n">
         <v>5</v>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>Obras e Instalações</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17575,21 +17575,21 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="F140" t="n">
-        <v>4001</v>
+        <v>4010</v>
       </c>
       <c r="G140" t="n">
-        <v>3002</v>
+        <v>4302</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>SESANA</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -17636,19 +17636,19 @@
         <v>0</v>
       </c>
       <c r="V140" t="n">
-        <v>1000</v>
+        <v>600437</v>
       </c>
       <c r="W140" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>16295665</v>
       </c>
       <c r="Y140" t="n">
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>1000</v>
+        <v>16896102</v>
       </c>
       <c r="AA140" t="n">
         <v>5</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="AD140" t="inlineStr">
         <is>
-          <t>Sesana - Reformas</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="AE140" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="F141" t="n">
-        <v>4010</v>
+        <v>4001</v>
       </c>
       <c r="G141" t="n">
-        <v>4426</v>
+        <v>3002</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44905100</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>40816540.35</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -17735,43 +17735,43 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>40640152.52</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>19947440.86</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>154812784.17</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>115924287.71</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>121364000.1</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>134865343.31</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>5439712.39</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>166077092</v>
+        <v>1000</v>
       </c>
       <c r="W141" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="X141" t="n">
-        <v>5735947</v>
+        <v>0</v>
       </c>
       <c r="Y141" t="n">
         <v>0</v>
       </c>
       <c r="Z141" t="n">
-        <v>171813039</v>
+        <v>1000</v>
       </c>
       <c r="AA141" t="n">
         <v>5</v>
@@ -17784,12 +17784,12 @@
       </c>
       <c r="AD141" t="inlineStr">
         <is>
-          <t>SESANA - Políticas</t>
+          <t>Sesana - Reformas</t>
         </is>
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Obras e Instalações</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17840,16 +17840,16 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33503900</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>40916913.71</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -17858,43 +17858,43 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>40640152.52</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>19947440.86</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>157005102.66</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>118116606.21</v>
       </c>
       <c r="S142" t="n">
-        <v>0</v>
+        <v>123556318.6</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>137057661.8</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>5439712.39</v>
       </c>
       <c r="V142" t="n">
-        <v>2000</v>
+        <v>166077092</v>
       </c>
       <c r="W142" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>5735947</v>
       </c>
       <c r="Y142" t="n">
         <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>2000</v>
+        <v>171813039</v>
       </c>
       <c r="AA142" t="n">
         <v>5</v>
@@ -17912,17 +17912,17 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Contratação PJ sem Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -18005,10 +18005,10 @@
         <v>0</v>
       </c>
       <c r="V143" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="W143" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="X143" t="n">
         <v>0</v>
@@ -18017,7 +18017,7 @@
         <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>11298</v>
+        <v>2000</v>
       </c>
       <c r="AA143" t="n">
         <v>5</v>
@@ -18040,12 +18040,12 @@
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
+          <t>PMSP-SMDU/CIDADE SOLIDÁRIA</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18086,16 +18086,16 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>33903200</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="K144" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -18104,43 +18104,43 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5410565.4</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>58907113.6</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>29453556.8</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>136889022</v>
+        <v>11298</v>
       </c>
       <c r="W144" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="X144" t="n">
-        <v>4727853</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="n">
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>141616875</v>
+        <v>11298</v>
       </c>
       <c r="AA144" t="n">
         <v>5</v>
@@ -18158,17 +18158,17 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>Cestas Básicas</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>PMSP-SMDHC-Fundo Munic.de Abastecimento Alimentar de São Paulo-FAASP</t>
         </is>
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903200</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>4042120.9</v>
+        <v>5410565.4</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18227,43 +18227,43 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2664000</v>
+        <v>5410565.4</v>
       </c>
       <c r="O145" t="n">
-        <v>180000</v>
+        <v>29453556.8</v>
       </c>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>32473650</v>
+        <v>58907113.6</v>
       </c>
       <c r="R145" t="n">
-        <v>32287200</v>
+        <v>29453556.8</v>
       </c>
       <c r="S145" t="n">
-        <v>32287200</v>
+        <v>29453556.8</v>
       </c>
       <c r="T145" t="n">
-        <v>32293650</v>
+        <v>29453556.8</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
       </c>
       <c r="V145" t="n">
-        <v>79443026</v>
+        <v>136889022</v>
       </c>
       <c r="W145" t="n">
-        <v>83642123</v>
+        <v>141616875</v>
       </c>
       <c r="X145" t="n">
-        <v>2792377</v>
+        <v>4727853</v>
       </c>
       <c r="Y145" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>82235403</v>
+        <v>141616875</v>
       </c>
       <c r="AA145" t="n">
         <v>5</v>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Cestas Básicas</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18337,11 +18337,11 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>4618120.9</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -18350,43 +18350,43 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2664000</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>493022.28</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>79936048.28</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>32600222.28</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>32600222.28</v>
       </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>79443026</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>2000</v>
+        <v>79443026</v>
       </c>
       <c r="W146" t="n">
-        <v>2000</v>
+        <v>83642123</v>
       </c>
       <c r="X146" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="Z146" t="n">
-        <v>2000</v>
+        <v>82235403</v>
       </c>
       <c r="AA146" t="n">
         <v>5</v>
@@ -18409,12 +18409,12 @@
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>33913900</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -18470,7 +18470,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -18482,25 +18482,25 @@
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>1406720</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
       </c>
       <c r="V147" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="W147" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X147" t="n">
         <v>0</v>
@@ -18509,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>1406720</v>
+        <v>2000</v>
       </c>
       <c r="AA147" t="n">
         <v>5</v>
@@ -18527,29 +18527,29 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>Transferência entre Órgãos</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>Recursos não vinculados de Impostos</t>
+          <t>Repasse nº 970993/2025-Banco de Alimentos</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>FAASP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -18563,22 +18563,22 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>122</v>
+        <v>422</v>
       </c>
       <c r="F148" t="n">
-        <v>4004</v>
+        <v>4010</v>
       </c>
       <c r="G148" t="n">
-        <v>2803</v>
+        <v>4426</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>33903000</t>
+          <t>33913900</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -18587,13 +18587,13 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="N148" t="n">
         <v>0</v>
@@ -18605,25 +18605,25 @@
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="S148" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>1406720</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="W148" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X148" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>3000</v>
+        <v>1406720</v>
       </c>
       <c r="AA148" t="n">
         <v>5</v>
@@ -18640,17 +18640,17 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>Segurança Alimentar</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
         <is>
-          <t>Conselho</t>
+          <t>SESANA - Políticas</t>
         </is>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>Material de Consumo</t>
+          <t>Transferência entre Órgãos</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>33903900</t>
+          <t>33903000</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -18743,10 +18743,10 @@
         <v>0</v>
       </c>
       <c r="V149" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="W149" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="X149" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
         <v>0</v>
       </c>
       <c r="Z149" t="n">
-        <v>6245</v>
+        <v>3000</v>
       </c>
       <c r="AA149" t="n">
         <v>5</v>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>Contratação PJ com Fins Lucrativos</t>
+          <t>Material de Consumo</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18809,22 +18809,22 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F150" t="n">
-        <v>4002</v>
+        <v>4004</v>
       </c>
       <c r="G150" t="n">
-        <v>1220</v>
+        <v>2803</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>DTIC</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>44904000</t>
+          <t>33903900</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -18866,10 +18866,10 @@
         <v>0</v>
       </c>
       <c r="V150" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="W150" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="X150" t="n">
         <v>0</v>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>1000</v>
+        <v>6245</v>
       </c>
       <c r="AA150" t="n">
         <v>5</v>
@@ -18886,17 +18886,17 @@
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Tecnologia</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>DTIC - Desenvolvimento</t>
+          <t>Conselho</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
+          <t>Contratação PJ com Fins Lucrativos</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -18932,27 +18932,27 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>422</v>
+        <v>126</v>
       </c>
       <c r="F151" t="n">
-        <v>4019</v>
+        <v>4002</v>
       </c>
       <c r="G151" t="n">
-        <v>6160</v>
+        <v>1220</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>33503900</t>
+          <t>44904000</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>0004</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -18989,10 +18989,10 @@
         <v>0</v>
       </c>
       <c r="V151" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W151" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X151" t="n">
         <v>0</v>
@@ -19001,7 +19001,7 @@
         <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA151" t="n">
         <v>5</v>
@@ -19009,27 +19009,27 @@
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Criança e Adolescente</t>
+          <t>Tecnologia</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
         <is>
-          <t>FUMCAD</t>
+          <t>DTIC - Desenvolvimento</t>
         </is>
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>Contratação PJ sem Fins Lucrativos</t>
+          <t>Serviços de Tecnologia da Informação e Comunicação Permanente - PJ</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>Recursos do FUMCAD desvinculados</t>
+          <t>Recursos não vinculados de Impostos</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>25/02/2026 07:09:50</t>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>
@@ -19075,11 +19075,11 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>0958</t>
+          <t>0004</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>13758108.3</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -19088,34 +19088,34 @@
         <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>9072713.01</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>3068431.98</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>35448208.44</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>32116802.57</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>33729566.67</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>32379776.46</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>1612764.1</v>
+        <v>0</v>
       </c>
       <c r="V152" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="W152" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="X152" t="n">
         <v>0</v>
@@ -19124,7 +19124,7 @@
         <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>61292510</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>5</v>
@@ -19147,12 +19147,135 @@
       </c>
       <c r="AF152" t="inlineStr">
         <is>
+          <t>Recursos do FUMCAD desvinculados</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>26/02/2026 07:05:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>422</v>
+      </c>
+      <c r="F153" t="n">
+        <v>4019</v>
+      </c>
+      <c r="G153" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>33503900</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>0958</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>15284010.55</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>10331685.27</v>
+      </c>
+      <c r="O153" t="n">
+        <v>3068431.98</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>35448208.44</v>
+      </c>
+      <c r="R153" t="n">
+        <v>32116802.57</v>
+      </c>
+      <c r="S153" t="n">
+        <v>33729566.67</v>
+      </c>
+      <c r="T153" t="n">
+        <v>32379776.46</v>
+      </c>
+      <c r="U153" t="n">
+        <v>1612764.1</v>
+      </c>
+      <c r="V153" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="W153" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>61292510</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Criança e Adolescente</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>FUMCAD</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>Contratação PJ sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
           <t>PMSP-SMDHC/FUMCAD</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>25/02/2026 07:09:50</t>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>26/02/2026 07:05:23</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>535673.5699999999</v>
+        <v>1443170.97</v>
       </c>
       <c r="O3" t="n">
         <v>21963.73</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>251299.99</v>
+        <v>279714.99</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -3962,22 +3962,22 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2164954.67</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5377087.17</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3212132.5</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3212132.5</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3212132.5</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
         <v>40624.92</v>
       </c>
       <c r="O30" t="n">
-        <v>2810.98</v>
+        <v>3160.42</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -4094,13 +4094,13 @@
         <v>17186912.55</v>
       </c>
       <c r="R30" t="n">
-        <v>16569256.04</v>
+        <v>16575976.04</v>
       </c>
       <c r="S30" t="n">
-        <v>16575828.69</v>
+        <v>16582548.69</v>
       </c>
       <c r="T30" t="n">
-        <v>17184101.57</v>
+        <v>17183752.13</v>
       </c>
       <c r="U30" t="n">
         <v>6572.65</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2564.77</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4337,16 +4337,16 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>281044.11</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>281044.11</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>281044.11</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>281044.11</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>31441.75</v>
+        <v>40941.75</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5690,16 +5690,16 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>3739123.62</v>
+        <v>3745528.66</v>
       </c>
       <c r="R43" t="n">
-        <v>3126496.8</v>
+        <v>3130777.22</v>
       </c>
       <c r="S43" t="n">
-        <v>3126496.8</v>
+        <v>3130777.22</v>
       </c>
       <c r="T43" t="n">
-        <v>3739123.62</v>
+        <v>3745528.66</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6797,16 +6797,16 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5686750</v>
+        <v>11245942.1</v>
       </c>
       <c r="R52" t="n">
-        <v>5495750</v>
+        <v>11054942.1</v>
       </c>
       <c r="S52" t="n">
-        <v>10991500</v>
+        <v>16550692.1</v>
       </c>
       <c r="T52" t="n">
-        <v>5686750</v>
+        <v>11245942.1</v>
       </c>
       <c r="U52" t="n">
         <v>5495750</v>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9011,16 +9011,16 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>483609.93</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>483609.93</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>483609.93</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>483609.93</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>254990.22</v>
+        <v>255716.54</v>
       </c>
       <c r="R71" t="n">
         <v>131366.56</v>
@@ -9143,7 +9143,7 @@
         <v>131366.56</v>
       </c>
       <c r="T71" t="n">
-        <v>254414.22</v>
+        <v>255140.54</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14177,16 +14177,16 @@
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>519437</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>485922.72</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>485922.72</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>519437</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14294,19 +14294,19 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>1621238.15</v>
+        <v>1621398.15</v>
       </c>
       <c r="P113" t="n">
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>5048475.3</v>
+        <v>5048635.3</v>
       </c>
       <c r="R113" t="n">
-        <v>1291768.13</v>
+        <v>2659928.13</v>
       </c>
       <c r="S113" t="n">
-        <v>1292088.13</v>
+        <v>2660248.13</v>
       </c>
       <c r="T113" t="n">
         <v>3427237.15</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15284,16 +15284,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>364021.94</v>
+        <v>475003.19</v>
       </c>
       <c r="R121" t="n">
-        <v>57214.44</v>
+        <v>168195.69</v>
       </c>
       <c r="S121" t="n">
-        <v>114428.88</v>
+        <v>225410.13</v>
       </c>
       <c r="T121" t="n">
-        <v>364021.94</v>
+        <v>475003.19</v>
       </c>
       <c r="U121" t="n">
         <v>57214.44</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15401,22 +15401,22 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>566200</v>
+        <v>567299.17</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2854466.54</v>
+        <v>2866473.69</v>
       </c>
       <c r="R122" t="n">
-        <v>1738210.53</v>
+        <v>1739309.72</v>
       </c>
       <c r="S122" t="n">
-        <v>1738210.53</v>
+        <v>1739309.72</v>
       </c>
       <c r="T122" t="n">
-        <v>2288266.54</v>
+        <v>2299174.52</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15530,16 +15530,16 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>80000</v>
+        <v>80100</v>
       </c>
       <c r="R123" t="n">
-        <v>80000</v>
+        <v>80100</v>
       </c>
       <c r="S123" t="n">
-        <v>80000</v>
+        <v>80100</v>
       </c>
       <c r="T123" t="n">
-        <v>80000</v>
+        <v>80100</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16637,16 +16637,16 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>5013837.31</v>
+        <v>5032621.72</v>
       </c>
       <c r="R132" t="n">
-        <v>543230.86</v>
+        <v>543510.86</v>
       </c>
       <c r="S132" t="n">
-        <v>543230.86</v>
+        <v>543510.86</v>
       </c>
       <c r="T132" t="n">
-        <v>5013286.23</v>
+        <v>5032070.64</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>40916913.71</v>
+        <v>40920413.71</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -17858,10 +17858,10 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>40640152.52</v>
+        <v>40713514.42</v>
       </c>
       <c r="O142" t="n">
-        <v>19947440.86</v>
+        <v>20385904.54</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -17876,7 +17876,7 @@
         <v>123556318.6</v>
       </c>
       <c r="T142" t="n">
-        <v>137057661.8</v>
+        <v>136619198.12</v>
       </c>
       <c r="U142" t="n">
         <v>5439712.39</v>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>5410565.4</v>
+        <v>10332515.4</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>4618120.9</v>
+        <v>6058120.9</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -18350,22 +18350,22 @@
         <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2664000</v>
+        <v>2754000</v>
       </c>
       <c r="O146" t="n">
-        <v>493022.28</v>
+        <v>937022.28</v>
       </c>
       <c r="P146" t="n">
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>79936048.28</v>
+        <v>80380048.28</v>
       </c>
       <c r="R146" t="n">
-        <v>32600222.28</v>
+        <v>33044222.28</v>
       </c>
       <c r="S146" t="n">
-        <v>32600222.28</v>
+        <v>33044222.28</v>
       </c>
       <c r="T146" t="n">
         <v>79443026</v>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>26/02/2026 07:05:23</t>
+          <t>27/02/2026 06:58:39</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202602.xlsx
+++ b/base_despesas/2026/despesas_202602.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1844144.91</v>
+        <v>1931102.91</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2878192.65</v>
+        <v>5563443.54</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2878192.65</v>
+        <v>5563443.54</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1016,16 +1016,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2878192.65</v>
+        <v>5563443.54</v>
       </c>
       <c r="R5" t="n">
-        <v>2878192.65</v>
+        <v>5563443.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2878192.65</v>
+        <v>5563443.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2878192.65</v>
+        <v>5563443.54</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11257.26</v>
+        <v>12902.01</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1508,16 +1508,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>279714.99</v>
+        <v>293917.71</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>11905366.24</v>
+        <v>11915477.34</v>
       </c>
       <c r="R10" t="n">
-        <v>7401759.09</v>
+        <v>7409380.19</v>
       </c>
       <c r="S10" t="n">
-        <v>7415547.98</v>
+        <v>7423169.08</v>
       </c>
       <c r="T10" t="n">
-        <v>11338980.03</v>
+        <v>11349091.13</v>
       </c>
       <c r="U10" t="n">
         <v>13788.89</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>107.79</v>
+        <v>1873.93</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>469185.6</v>
+        <v>919981.36</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>469185.6</v>
+        <v>919981.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>469185.6</v>
+        <v>919981.36</v>
       </c>
       <c r="R12" t="n">
-        <v>469185.6</v>
+        <v>919981.36</v>
       </c>
       <c r="S12" t="n">
-        <v>469185.6</v>
+        <v>919981.36</v>
       </c>
       <c r="T12" t="n">
-        <v>469185.6</v>
+        <v>919981.36</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>19795.55</v>
+        <v>47137.94</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>19795.55</v>
+        <v>47137.94</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2123,16 +2123,16 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>19795.55</v>
+        <v>47137.94</v>
       </c>
       <c r="R14" t="n">
-        <v>19795.55</v>
+        <v>47137.94</v>
       </c>
       <c r="S14" t="n">
-        <v>19795.55</v>
+        <v>47137.94</v>
       </c>
       <c r="T14" t="n">
-        <v>19795.55</v>
+        <v>47137.94</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>40389.32</v>
+        <v>434637.68</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         <v>9180</v>
       </c>
       <c r="Q28" t="n">
-        <v>2034582.74</v>
+        <v>2035080.12</v>
       </c>
       <c r="R28" t="n">
         <v>1485288.62</v>
@@ -3854,7 +3854,7 @@
         <v>1597671.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1832707.3</v>
+        <v>1833204.68</v>
       </c>
       <c r="U28" t="n">
         <v>112383.13</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>376030.34</v>
+        <v>377205.83</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>40624.92</v>
+        <v>47624.92</v>
       </c>
       <c r="O30" t="n">
         <v>3160.42</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>275631.58</v>
+        <v>275797.2</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5570,10 +5570,10 @@
         <v>1866731.38</v>
       </c>
       <c r="R42" t="n">
-        <v>229579.78</v>
+        <v>1460688.16</v>
       </c>
       <c r="S42" t="n">
-        <v>229579.78</v>
+        <v>1460688.16</v>
       </c>
       <c r="T42" t="n">
         <v>1460688.16</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>40941.75</v>
+        <v>44093.28</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5690,16 +5690,16 @@
         <v>186346</v>
       </c>
       <c r="Q43" t="n">
-        <v>3745528.66</v>
+        <v>3775528.66</v>
       </c>
       <c r="R43" t="n">
-        <v>3130777.22</v>
+        <v>3160777.22</v>
       </c>
       <c r="S43" t="n">
-        <v>3130777.22</v>
+        <v>3160777.22</v>
       </c>
       <c r="T43" t="n">
-        <v>3745528.66</v>
+        <v>3775528.66</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6305,16 +6305,16 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>156730.89</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>156730.89</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>156730.89</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>156730.89</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -7181,13 +7181,13 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W55" t="n">
         <v>200000</v>
       </c>
       <c r="X55" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -7427,13 +7427,13 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="W57" t="n">
         <v>100000</v>
       </c>
       <c r="X57" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -7550,13 +7550,13 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="W58" t="n">
         <v>100000</v>
       </c>
       <c r="X58" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -7673,13 +7673,13 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="W59" t="n">
         <v>350000</v>
       </c>
       <c r="X59" t="n">
-        <v>350000</v>
+        <v>700000</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W61" t="n">
         <v>200000</v>
       </c>
       <c r="X61" t="n">
-        <v>200000</v>
+        <v>400000</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>4600000</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -8042,13 +8042,13 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>2300000</v>
       </c>
       <c r="W62" t="n">
         <v>2300000</v>
       </c>
       <c r="X62" t="n">
-        <v>2300000</v>
+        <v>4600000</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9128,22 +9128,22 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>576</v>
+        <v>1103.06</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>255716.54</v>
+        <v>257297.72</v>
       </c>
       <c r="R71" t="n">
-        <v>131366.56</v>
+        <v>132420.68</v>
       </c>
       <c r="S71" t="n">
-        <v>131366.56</v>
+        <v>132420.68</v>
       </c>
       <c r="T71" t="n">
-        <v>255140.54</v>
+        <v>256194.66</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -9518,13 +9518,13 @@
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="W74" t="n">
         <v>100000</v>
       </c>
       <c r="X74" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -9995,16 +9995,16 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13193,16 +13193,16 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>240000</v>
+        <v>286118.97</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>46118.97</v>
       </c>
       <c r="T104" t="n">
-        <v>240000</v>
+        <v>286118.97</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13316,16 +13316,16 @@
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>202849.86</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13433,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>216540.94</v>
+        <v>216553.88</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -13442,13 +13442,13 @@
         <v>453625.94</v>
       </c>
       <c r="R106" t="n">
-        <v>230326.94</v>
+        <v>230854</v>
       </c>
       <c r="S106" t="n">
-        <v>230326.94</v>
+        <v>230854</v>
       </c>
       <c r="T106" t="n">
-        <v>237085</v>
+        <v>237072.06</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>1221823</v>
+        <v>2308010.51</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14036,7 +14036,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>656</v>
+        <v>984</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>2028.89</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>5027120.48</v>
+        <v>5478096.41</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15284,16 +15284,16 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>475003.19</v>
+        <v>1074549.58</v>
       </c>
       <c r="R121" t="n">
-        <v>168195.69</v>
+        <v>1074549.58</v>
       </c>
       <c r="S121" t="n">
-        <v>225410.13</v>
+        <v>1131764.02</v>
       </c>
       <c r="T121" t="n">
-        <v>475003.19</v>
+        <v>1074549.58</v>
       </c>
       <c r="U121" t="n">
         <v>57214.44</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15389,7 +15389,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>24906.96</v>
+        <v>25026.76</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -15401,22 +15401,22 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>567299.17</v>
+        <v>743505.8100000001</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2866473.69</v>
+        <v>3251361.85</v>
       </c>
       <c r="R122" t="n">
-        <v>1739309.72</v>
+        <v>1951991.24</v>
       </c>
       <c r="S122" t="n">
-        <v>1739309.72</v>
+        <v>1951991.24</v>
       </c>
       <c r="T122" t="n">
-        <v>2299174.52</v>
+        <v>2507856.04</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15773,7 +15773,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>220000</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -15791,13 +15791,13 @@
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="W125" t="n">
         <v>110000</v>
       </c>
       <c r="X125" t="n">
-        <v>110000</v>
+        <v>220000</v>
       </c>
       <c r="Y125" t="n">
         <v>0</v>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -15914,13 +15914,13 @@
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="W126" t="n">
         <v>100000</v>
       </c>
       <c r="X126" t="n">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="Y126" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>3595409.86</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>179.7</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -16640,10 +16640,10 @@
         <v>5032621.72</v>
       </c>
       <c r="R132" t="n">
-        <v>543510.86</v>
+        <v>551310.86</v>
       </c>
       <c r="S132" t="n">
-        <v>543510.86</v>
+        <v>551310.86</v>
       </c>
       <c r="T132" t="n">
         <v>5032070.64</v>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17249,7 +17249,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>55747.3</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
@@ -17267,13 +17267,13 @@
         <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>27873.65</v>
       </c>
       <c r="W137" t="n">
         <v>100000</v>
       </c>
       <c r="X137" t="n">
-        <v>100000</v>
+        <v>127873.65</v>
       </c>
       <c r="Y137" t="n">
         <v>0</v>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>40920413.71</v>
+        <v>41561876.54</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -17858,7 +17858,7 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>40713514.42</v>
+        <v>40816540.35</v>
       </c>
       <c r="O142" t="n">
         <v>20385904.54</v>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>10332515.4</v>
+        <v>12793490.4</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>6058120.9</v>
+        <v>7288668.99</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
@@ -19211,7 +19211,7 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>10331685.27</v>
+        <v>10622477.2</v>
       </c>
       <c r="O153" t="n">
         <v>3068431.98</v>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>27/02/2026 06:58:39</t>
+          <t>28/02/2026 06:40:53</t>
         </is>
       </c>
     </row>
